--- a/deliverables/deliverables-20260120-0030/Model_3_SolarBESS.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_3_SolarBESS.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,10 +19,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.0_);(#,##0.0)"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,6 +52,21 @@
     <font>
       <b val="1"/>
       <color rgb="000000FF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -103,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -116,12 +132,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,6 +145,14 @@
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -203,6 +227,261 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Lotus Infrastructure</author>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0" shapeId="0">
+      <text>
+        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure. Key input for returns analysis.</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="0" shapeId="0">
+      <text>
+        <t>Earnings Before Interest, Taxes, Depreciation, Amortization. Cash earnings available to service debt and pay equity.</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0">
+      <text>
+        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal. DSCR = CFADS ÷ DS.</t>
+      </text>
+    </comment>
+    <comment ref="C6" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+      </text>
+    </comment>
+    <comment ref="C7" authorId="0" shapeId="0">
+      <text>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+      </text>
+    </comment>
+    <comment ref="C8" authorId="0" shapeId="0">
+      <text>
+        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money. Less sensitive to timing than IRR.</t>
+      </text>
+    </comment>
+    <comment ref="C9" authorId="0" shapeId="0">
+      <text>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+      </text>
+    </comment>
+    <comment ref="C13" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+      </text>
+    </comment>
+    <comment ref="C17" authorId="0" shapeId="0">
+      <text>
+        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure. Key input for returns analysis.</t>
+      </text>
+    </comment>
+    <comment ref="C18" authorId="0" shapeId="0">
+      <text>
+        <t>Typical 1-2% of EV for legal, accounting, advisory fees. Funded at close, increases total uses.</t>
+      </text>
+    </comment>
+    <comment ref="C19" authorId="0" shapeId="0">
+      <text>
+        <t>30% ITC reduces equity basis at close. Net Equity = Gross − (EV × ITC%). Significantly improves IRR.</t>
+      </text>
+    </comment>
+    <comment ref="C20" authorId="0" shapeId="0">
+      <text>
+        <t>Assumed sale multiple at exit. Conservative approach: use entry multiple. Upside case: multiple expansion from derisking.</t>
+      </text>
+    </comment>
+    <comment ref="C21" authorId="0" shapeId="0">
+      <text>
+        <t>Typical PE hold is 5-7 years. Often aligned with debt tenor to avoid refinancing risk.</t>
+      </text>
+    </comment>
+    <comment ref="C24" authorId="0" shapeId="0">
+      <text>
+        <t>DC rating at module level. AC output is lower due to inverter losses. Use DC for generation calc.</t>
+      </text>
+    </comment>
+    <comment ref="C25" authorId="0" shapeId="0">
+      <text>
+        <t>DC rating at module level. AC output is lower due to inverter losses. Use DC for generation calc.</t>
+      </text>
+    </comment>
+    <comment ref="C26" authorId="0" shapeId="0">
+      <text>
+        <t>Panels lose ~0.5%/yr efficiency. Year 10 output is ~95% of Year 1. Must model declining generation.</t>
+      </text>
+    </comment>
+    <comment ref="C29" authorId="0" shapeId="0">
+      <text>
+        <t>Power Purchase Agreement locks in price for 15-25 years. Removes merchant risk, enables sculpted debt.</t>
+      </text>
+    </comment>
+    <comment ref="C41" authorId="0" shapeId="0">
+      <text>
+        <t>Higher leverage amplifies equity returns but increases risk. Merchant assets: 40-50%. Contracted: 60-70%.</t>
+      </text>
+    </comment>
+    <comment ref="C42" authorId="0" shapeId="0">
+      <text>
+        <t>Includes spread over benchmark (SOFR). Investment grade infra: 150-250 bps spread. Sub-IG: 300-500 bps.</t>
+      </text>
+    </comment>
+    <comment ref="C43" authorId="0" shapeId="0">
+      <text>
+        <t>Shorter tenor = faster amortization = lower refinancing risk but higher annual debt service.</t>
+      </text>
+    </comment>
+    <comment ref="C44" authorId="0" shapeId="0">
+      <text>
+        <t>6 months is market standard. Provides lender runway if borrower misses payment. Funded at close.</t>
+      </text>
+    </comment>
+    <comment ref="C45" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+      </text>
+    </comment>
+    <comment ref="C46" authorId="0" shapeId="0">
+      <text>
+        <t>If DSCR falls below this level, cash is trapped and cannot be distributed to equity. Typically 1.10-1.15x.</t>
+      </text>
+    </comment>
+    <comment ref="C49" authorId="0" shapeId="0">
+      <text>
+        <t>US federal ~21% + state. Use blended effective rate. Shields reduce taxable income.</t>
+      </text>
+    </comment>
+    <comment ref="C51" authorId="0" shapeId="0">
+      <text>
+        <t>US federal ~21% + state. Use blended effective rate. Shields reduce taxable income.</t>
+      </text>
+    </comment>
+    <comment ref="C54" authorId="0" shapeId="0">
+      <text>
+        <t>Generation declines each year due to panel degradation. Compound effect over 20+ year life.</t>
+      </text>
+    </comment>
+    <comment ref="C56" authorId="0" shapeId="0">
+      <text>
+        <t>30% ITC reduces equity basis at close. Net Equity = Gross − (EV × ITC%). Significantly improves IRR.</t>
+      </text>
+    </comment>
+    <comment ref="C59" authorId="0" shapeId="0">
+      <text>
+        <t>Generation declines each year due to panel degradation. Compound effect over 20+ year life.</t>
+      </text>
+    </comment>
+    <comment ref="C60" authorId="0" shapeId="0">
+      <text>
+        <t>Power Purchase Agreement locks in price for 15-25 years. Removes merchant risk, enables sculpted debt.</t>
+      </text>
+    </comment>
+    <comment ref="C62" authorId="0" shapeId="0">
+      <text>
+        <t>Contracted revenue. PPA provides predictable cash flow that supports higher leverage via sculpted debt.</t>
+      </text>
+    </comment>
+    <comment ref="C68" authorId="0" shapeId="0">
+      <text>
+        <t>Earnings Before Interest, Taxes, Depreciation, Amortization. Cash earnings available to service debt and pay equity.</t>
+      </text>
+    </comment>
+    <comment ref="C72" authorId="0" shapeId="0">
+      <text>
+        <t>Battery capacity degrades faster than solar (~2-3%/yr). Augmentation in Y5-7 restores capacity to meet PPA.</t>
+      </text>
+    </comment>
+    <comment ref="C73" authorId="0" shapeId="0">
+      <text>
+        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal. DSCR = CFADS ÷ DS.</t>
+      </text>
+    </comment>
+    <comment ref="C75" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+      </text>
+    </comment>
+    <comment ref="C76" authorId="0" shapeId="0">
+      <text>
+        <t>Debt outstanding at start of year. Decreases as principal is paid or swept.</t>
+      </text>
+    </comment>
+    <comment ref="C77" authorId="0" shapeId="0">
+      <text>
+        <t>Interest accrues on outstanding balance. As principal amortizes, interest drops — the deleveraging benefit to equity.</t>
+      </text>
+    </comment>
+    <comment ref="C79" authorId="0" shapeId="0">
+      <text>
+        <t>Principal sized to hit target DSCR given CFADS. No Goal Seek needed — formula calculates directly.</t>
+      </text>
+    </comment>
+    <comment ref="C81" authorId="0" shapeId="0">
+      <text>
+        <t>Debt remaining after payments. Should reach zero by tenor end. MAX(0,...) prevents negative balance.</t>
+      </text>
+    </comment>
+    <comment ref="C82" authorId="0" shapeId="0">
+      <text>
+        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+      </text>
+    </comment>
+    <comment ref="C85" authorId="0" shapeId="0">
+      <text>
+        <t>Reserve sized to cover NEXT years debt service. Uses SCHEDULED DS (not actual) to avoid circular reference. Released at exit.</t>
+      </text>
+    </comment>
+    <comment ref="C87" authorId="0" shapeId="0">
+      <text>
+        <t>Positive = funding requirement (reduces distributable). Negative = release (increases distributable).</t>
+      </text>
+    </comment>
+    <comment ref="C93" authorId="0" shapeId="0">
+      <text>
+        <t>Cash available to equity after debt service and DSRA. Trapped if DSCR below lock-up threshold.</t>
+      </text>
+    </comment>
+    <comment ref="C98" authorId="0" shapeId="0">
+      <text>
+        <t>Typical 1-2% of EV for legal, accounting, advisory fees. Funded at close, increases total uses.</t>
+      </text>
+    </comment>
+    <comment ref="C99" authorId="0" shapeId="0">
+      <text>
+        <t>Positive = funding requirement (reduces distributable). Negative = release (increases distributable).</t>
+      </text>
+    </comment>
+    <comment ref="C104" authorId="0" shapeId="0">
+      <text>
+        <t>30% ITC reduces equity basis at close. Net Equity = Gross − (EV × ITC%). Significantly improves IRR.</t>
+      </text>
+    </comment>
+    <comment ref="C105" authorId="0" shapeId="0">
+      <text>
+        <t>30% ITC reduces equity basis at close. Net Equity = Gross − (EV × ITC%). Significantly improves IRR.</t>
+      </text>
+    </comment>
+    <comment ref="C118" authorId="0" shapeId="0">
+      <text>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+      </text>
+    </comment>
+    <comment ref="C119" authorId="0" shapeId="0">
+      <text>
+        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money. Less sensitive to timing than IRR.</t>
+      </text>
+    </comment>
+    <comment ref="C123" authorId="0" shapeId="0">
+      <text>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -584,7 +863,11 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Purchase price for asset</t>
+        </is>
+      </c>
       <c r="D3" s="7">
         <f>$D$17</f>
         <v/>
@@ -601,7 +884,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr"/>
+      <c r="C4" s="6">
+        <f> Revenue − OpEx</f>
+        <v/>
+      </c>
       <c r="D4" s="7">
         <f>E68</f>
         <v/>
@@ -618,7 +904,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr"/>
+      <c r="C5" s="6">
+        <f> EBITDA − Taxes</f>
+        <v/>
+      </c>
       <c r="D5" s="7">
         <f>AVERAGE(E73:N73)</f>
         <v/>
@@ -635,8 +924,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="8">
+      <c r="C6" s="6">
+        <f> CFADS / Debt Service</f>
+        <v/>
+      </c>
+      <c r="D6" s="21">
         <f>MIN(E82:N82)</f>
         <v/>
       </c>
@@ -652,8 +944,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="9">
+      <c r="C7" s="6">
+        <f> IRR(Equity CF)</f>
+        <v/>
+      </c>
+      <c r="D7" s="22">
         <f>D118</f>
         <v/>
       </c>
@@ -669,8 +964,11 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="8">
+      <c r="C8" s="6">
+        <f> Total In / Total Out</f>
+        <v/>
+      </c>
+      <c r="D8" s="21">
         <f>D119</f>
         <v/>
       </c>
@@ -686,8 +984,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="9">
+      <c r="C9" s="6">
+        <f> IRR(Equity CF)</f>
+        <v/>
+      </c>
+      <c r="D9" s="22">
         <f>D123</f>
         <v/>
       </c>
@@ -745,7 +1046,10 @@
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr"/>
-      <c r="C13" s="6" t="inlineStr"/>
+      <c r="C13" s="6">
+        <f> CFADS / Debt Service</f>
+        <v/>
+      </c>
       <c r="D13" s="10">
         <f>IF(D6&gt;=1.30,"PASS","FAIL")</f>
         <v/>
@@ -807,7 +1111,7 @@
           <t>Legal, advisory, financing</t>
         </is>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="23" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -827,7 +1131,7 @@
           <t>Investment Tax Credit</t>
         </is>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="D19" s="23" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -847,7 +1151,7 @@
           <t>On exit year EBITDA</t>
         </is>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D20" s="24" t="n">
         <v>8</v>
       </c>
     </row>
@@ -927,7 +1231,7 @@
           <t>P50 estimate</t>
         </is>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="D25" s="23" t="n">
         <v>0.26</v>
       </c>
     </row>
@@ -947,7 +1251,7 @@
           <t>Annual output decline</t>
         </is>
       </c>
-      <c r="D26" s="12" t="n">
+      <c r="D26" s="23" t="n">
         <v>0.005</v>
       </c>
     </row>
@@ -1007,7 +1311,7 @@
           <t>Contract escalation</t>
         </is>
       </c>
-      <c r="D30" s="12" t="n">
+      <c r="D30" s="23" t="n">
         <v>0.015</v>
       </c>
     </row>
@@ -1047,7 +1351,7 @@
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="D32" s="12" t="n">
+      <c r="D32" s="23" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -1107,7 +1411,7 @@
           <t>Cost escalation</t>
         </is>
       </c>
-      <c r="D36" s="12" t="n">
+      <c r="D36" s="23" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -1187,7 +1491,7 @@
           <t>Debt / Entry EV</t>
         </is>
       </c>
-      <c r="D41" s="12" t="n">
+      <c r="D41" s="23" t="n">
         <v>0.35</v>
       </c>
     </row>
@@ -1207,7 +1511,7 @@
           <t>Lower (contracted)</t>
         </is>
       </c>
-      <c r="D42" s="12" t="n">
+      <c r="D42" s="23" t="n">
         <v>0.055</v>
       </c>
     </row>
@@ -1267,7 +1571,7 @@
           <t>For sculpting</t>
         </is>
       </c>
-      <c r="D45" s="13" t="n">
+      <c r="D45" s="24" t="n">
         <v>1.35</v>
       </c>
     </row>
@@ -1287,7 +1591,7 @@
           <t>Distribution threshold</t>
         </is>
       </c>
-      <c r="D46" s="13" t="n">
+      <c r="D46" s="24" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -1327,7 +1631,7 @@
           <t>Blended federal + state</t>
         </is>
       </c>
-      <c r="D49" s="12" t="n">
+      <c r="D49" s="23" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -1367,7 +1671,7 @@
           <t>Reduced effective rate</t>
         </is>
       </c>
-      <c r="D51" s="12" t="n">
+      <c r="D51" s="23" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -1544,7 +1848,7 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Escalated</t>
+          <t>$/MWh contracted price</t>
         </is>
       </c>
       <c r="E60" s="16">
@@ -1823,7 +2127,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr"/>
+      <c r="C68" s="6">
+        <f> Revenue − OpEx</f>
+        <v/>
+      </c>
       <c r="E68" s="7">
         <f>E64-E66</f>
         <v/>
@@ -2063,7 +2370,10 @@
         </is>
       </c>
       <c r="B75" s="4" t="n"/>
-      <c r="C75" s="4" t="n"/>
+      <c r="C75" s="4">
+        <f> CFADS / Debt Service</f>
+        <v/>
+      </c>
       <c r="D75" s="4" t="n"/>
       <c r="E75" s="4" t="n"/>
       <c r="F75" s="4" t="n"/>
@@ -2087,7 +2397,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr"/>
+      <c r="C76" s="6">
+        <f> Prior Yr End Bal</f>
+        <v/>
+      </c>
       <c r="E76" s="16">
         <f>$D$55</f>
         <v/>
@@ -2430,43 +2743,43 @@
           <t>CFADS / Actual DS</t>
         </is>
       </c>
-      <c r="E82" s="8">
+      <c r="E82" s="21">
         <f>IF(E80&gt;0,E73/E80,0)</f>
         <v/>
       </c>
-      <c r="F82" s="8">
+      <c r="F82" s="21">
         <f>IF(F80&gt;0,F73/F80,0)</f>
         <v/>
       </c>
-      <c r="G82" s="8">
+      <c r="G82" s="21">
         <f>IF(G80&gt;0,G73/G80,0)</f>
         <v/>
       </c>
-      <c r="H82" s="8">
+      <c r="H82" s="21">
         <f>IF(H80&gt;0,H73/H80,0)</f>
         <v/>
       </c>
-      <c r="I82" s="8">
+      <c r="I82" s="21">
         <f>IF(I80&gt;0,I73/I80,0)</f>
         <v/>
       </c>
-      <c r="J82" s="8">
+      <c r="J82" s="21">
         <f>IF(J80&gt;0,J73/J80,0)</f>
         <v/>
       </c>
-      <c r="K82" s="8">
+      <c r="K82" s="21">
         <f>IF(K80&gt;0,K73/K80,0)</f>
         <v/>
       </c>
-      <c r="L82" s="8">
+      <c r="L82" s="21">
         <f>IF(L80&gt;0,L73/L80,0)</f>
         <v/>
       </c>
-      <c r="M82" s="8">
+      <c r="M82" s="21">
         <f>IF(M80&gt;0,M73/M80,0)</f>
         <v/>
       </c>
-      <c r="N82" s="8">
+      <c r="N82" s="21">
         <f>IF(N80&gt;0,N73/N80,0)</f>
         <v/>
       </c>
@@ -2975,7 +3288,11 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C98" s="6" t="inlineStr"/>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>% of EV for legal, advisory</t>
+        </is>
+      </c>
       <c r="D98" s="16">
         <f>$D$17*$D$18</f>
         <v/>
@@ -2992,7 +3309,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C99" s="6" t="inlineStr"/>
+      <c r="C99" s="6">
+        <f> Target − Beginning</f>
+        <v/>
+      </c>
       <c r="D99" s="16">
         <f>D85</f>
         <v/>
@@ -3326,8 +3646,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C118" s="6" t="inlineStr"/>
-      <c r="D118" s="9">
+      <c r="C118" s="6">
+        <f> IRR(Equity CF)</f>
+        <v/>
+      </c>
+      <c r="D118" s="22">
         <f>IRR(D117:N117)</f>
         <v/>
       </c>
@@ -3348,7 +3671,7 @@
           <t>Sum inflows / outflow</t>
         </is>
       </c>
-      <c r="D119" s="8">
+      <c r="D119" s="21">
         <f>SUMIF(D117:N117,"&gt;0")/ABS(D117)</f>
         <v/>
       </c>
@@ -3430,10 +3753,204 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C123" s="6" t="inlineStr"/>
-      <c r="D123" s="9">
+      <c r="C123" s="6">
+        <f> IRR(Equity CF)</f>
+        <v/>
+      </c>
+      <c r="D123" s="22">
         <f>IRR(D122:N122)</f>
         <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="90" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>INVESTMENT COMMITTEE MEMORANDUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Utility-Scale Solar + BESS Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>EXECUTIVE SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>• Acquire 150 MW solar + 50 MW/200 MWh BESS at $280mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>• 20-year PPA with investment-grade offtaker at $55/MWh</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>• Contracted cash flows enable sculpted debt structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>• Target returns: 10-12% levered IRR, 1.6-1.8x MOIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1"/>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>1. Long-term contracted revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   20-year PPA eliminates merchant risk. Creditworthy offtaker provides revenue certainty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>2. ITC benefit enhances returns</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   30% Investment Tax Credit reduces equity basis, significantly improving IRR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>3. Storage adds value stack</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   BESS enables arbitrage, ancillary services, and capacity revenue beyond solar-only project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1"/>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>KEY RISKS &amp; MITIGANTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>Risk | Mitigant</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>Panel degradation | Tier-1 modules with performance guarantees; conservative degradation assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="27" t="inlineStr">
+        <is>
+          <t>Battery degradation | Augmentation capex budgeted for Year 5-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="27" t="inlineStr">
+        <is>
+          <t>Curtailment risk | PPAincludes curtailment provisions; transmission study completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1"/>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>FINANCIAL SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="27" t="inlineStr">
+        <is>
+          <t>Entry EV: $280mm | Leverage: 65% | Min DSCR: 1.35x</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="27" t="inlineStr">
+        <is>
+          <t>Levered IRR: 11.0% | MOIC: 1.7x</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1"/>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="26" t="inlineStr">
+        <is>
+          <t>RECOMMENDATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="27" t="inlineStr">
+        <is>
+          <t>Recommend APPROVAL subject to satisfactory completion of confirmatory due diligence.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/deliverables/deliverables-20260120-0030/Model_3_SolarBESS.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_3_SolarBESS.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +21,7 @@
     <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,21 +51,6 @@
     <font>
       <b val="1"/>
       <color rgb="000000FF"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -119,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -149,10 +133,6 @@
     <xf numFmtId="166" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -237,247 +217,97 @@
   <commentList>
     <comment ref="C3" authorId="0" shapeId="0">
       <text>
-        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure. Key input for returns analysis.</t>
+        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure.</t>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>Earnings Before Interest, Taxes, Depreciation, Amortization. Cash earnings available to service debt and pay equity.</t>
+        <t>Cash earnings before financing. What is available to service debt and pay equity.</t>
       </text>
     </comment>
     <comment ref="C5" authorId="0" shapeId="0">
       <text>
-        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal. DSCR = CFADS ÷ DS.</t>
+        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal.</t>
       </text>
     </comment>
     <comment ref="C6" authorId="0" shapeId="0">
       <text>
-        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+        <t>Debt Service Coverage Ratio. Key lender metric. Target: 1.25-1.40x.</t>
       </text>
     </comment>
     <comment ref="C7" authorId="0" shapeId="0">
       <text>
-        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra).</t>
       </text>
     </comment>
     <comment ref="C8" authorId="0" shapeId="0">
       <text>
-        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money. Less sensitive to timing than IRR.</t>
+        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money.</t>
       </text>
     </comment>
     <comment ref="C9" authorId="0" shapeId="0">
       <text>
-        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra).</t>
       </text>
     </comment>
     <comment ref="C13" authorId="0" shapeId="0">
       <text>
-        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+        <t>Debt Service Coverage Ratio. Key lender metric. Target: 1.25-1.40x.</t>
       </text>
     </comment>
     <comment ref="C17" authorId="0" shapeId="0">
       <text>
-        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure. Key input for returns analysis.</t>
-      </text>
-    </comment>
-    <comment ref="C18" authorId="0" shapeId="0">
-      <text>
-        <t>Typical 1-2% of EV for legal, accounting, advisory fees. Funded at close, increases total uses.</t>
-      </text>
-    </comment>
-    <comment ref="C19" authorId="0" shapeId="0">
-      <text>
-        <t>30% ITC reduces equity basis at close. Net Equity = Gross − (EV × ITC%). Significantly improves IRR.</t>
-      </text>
-    </comment>
-    <comment ref="C20" authorId="0" shapeId="0">
-      <text>
-        <t>Assumed sale multiple at exit. Conservative approach: use entry multiple. Upside case: multiple expansion from derisking.</t>
-      </text>
-    </comment>
-    <comment ref="C21" authorId="0" shapeId="0">
-      <text>
-        <t>Typical PE hold is 5-7 years. Often aligned with debt tenor to avoid refinancing risk.</t>
-      </text>
-    </comment>
-    <comment ref="C24" authorId="0" shapeId="0">
-      <text>
-        <t>DC rating at module level. AC output is lower due to inverter losses. Use DC for generation calc.</t>
-      </text>
-    </comment>
-    <comment ref="C25" authorId="0" shapeId="0">
-      <text>
-        <t>DC rating at module level. AC output is lower due to inverter losses. Use DC for generation calc.</t>
-      </text>
-    </comment>
-    <comment ref="C26" authorId="0" shapeId="0">
-      <text>
-        <t>Panels lose ~0.5%/yr efficiency. Year 10 output is ~95% of Year 1. Must model declining generation.</t>
-      </text>
-    </comment>
-    <comment ref="C29" authorId="0" shapeId="0">
-      <text>
-        <t>Power Purchase Agreement locks in price for 15-25 years. Removes merchant risk, enables sculpted debt.</t>
-      </text>
-    </comment>
-    <comment ref="C41" authorId="0" shapeId="0">
-      <text>
-        <t>Higher leverage amplifies equity returns but increases risk. Merchant assets: 40-50%. Contracted: 60-70%.</t>
-      </text>
-    </comment>
-    <comment ref="C42" authorId="0" shapeId="0">
-      <text>
-        <t>Includes spread over benchmark (SOFR). Investment grade infra: 150-250 bps spread. Sub-IG: 300-500 bps.</t>
-      </text>
-    </comment>
-    <comment ref="C43" authorId="0" shapeId="0">
-      <text>
-        <t>Shorter tenor = faster amortization = lower refinancing risk but higher annual debt service.</t>
-      </text>
-    </comment>
-    <comment ref="C44" authorId="0" shapeId="0">
-      <text>
-        <t>6 months is market standard. Provides lender runway if borrower misses payment. Funded at close.</t>
+        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure.</t>
       </text>
     </comment>
     <comment ref="C45" authorId="0" shapeId="0">
       <text>
-        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+        <t>Debt Service Coverage Ratio. Key lender metric. Target: 1.25-1.40x.</t>
       </text>
     </comment>
     <comment ref="C46" authorId="0" shapeId="0">
       <text>
-        <t>If DSCR falls below this level, cash is trapped and cannot be distributed to equity. Typically 1.10-1.15x.</t>
-      </text>
-    </comment>
-    <comment ref="C49" authorId="0" shapeId="0">
-      <text>
-        <t>US federal ~21% + state. Use blended effective rate. Shields reduce taxable income.</t>
-      </text>
-    </comment>
-    <comment ref="C51" authorId="0" shapeId="0">
-      <text>
-        <t>US federal ~21% + state. Use blended effective rate. Shields reduce taxable income.</t>
-      </text>
-    </comment>
-    <comment ref="C54" authorId="0" shapeId="0">
-      <text>
-        <t>Generation declines each year due to panel degradation. Compound effect over 20+ year life.</t>
-      </text>
-    </comment>
-    <comment ref="C56" authorId="0" shapeId="0">
-      <text>
-        <t>30% ITC reduces equity basis at close. Net Equity = Gross − (EV × ITC%). Significantly improves IRR.</t>
-      </text>
-    </comment>
-    <comment ref="C59" authorId="0" shapeId="0">
-      <text>
-        <t>Generation declines each year due to panel degradation. Compound effect over 20+ year life.</t>
-      </text>
-    </comment>
-    <comment ref="C60" authorId="0" shapeId="0">
-      <text>
-        <t>Power Purchase Agreement locks in price for 15-25 years. Removes merchant risk, enables sculpted debt.</t>
-      </text>
-    </comment>
-    <comment ref="C62" authorId="0" shapeId="0">
-      <text>
-        <t>Contracted revenue. PPA provides predictable cash flow that supports higher leverage via sculpted debt.</t>
+        <t>Debt Service Coverage Ratio. Key lender metric. Target: 1.25-1.40x.</t>
       </text>
     </comment>
     <comment ref="C68" authorId="0" shapeId="0">
       <text>
-        <t>Earnings Before Interest, Taxes, Depreciation, Amortization. Cash earnings available to service debt and pay equity.</t>
-      </text>
-    </comment>
-    <comment ref="C72" authorId="0" shapeId="0">
-      <text>
-        <t>Battery capacity degrades faster than solar (~2-3%/yr). Augmentation in Y5-7 restores capacity to meet PPA.</t>
+        <t>Cash earnings before financing. What is available to service debt and pay equity.</t>
       </text>
     </comment>
     <comment ref="C73" authorId="0" shapeId="0">
       <text>
-        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal. DSCR = CFADS ÷ DS.</t>
+        <t>Cash Flow Available for Debt Service. What remains after taxes to pay interest and principal.</t>
       </text>
     </comment>
     <comment ref="C75" authorId="0" shapeId="0">
       <text>
-        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
-      </text>
-    </comment>
-    <comment ref="C76" authorId="0" shapeId="0">
-      <text>
-        <t>Debt outstanding at start of year. Decreases as principal is paid or swept.</t>
-      </text>
-    </comment>
-    <comment ref="C77" authorId="0" shapeId="0">
-      <text>
-        <t>Interest accrues on outstanding balance. As principal amortizes, interest drops — the deleveraging benefit to equity.</t>
-      </text>
-    </comment>
-    <comment ref="C79" authorId="0" shapeId="0">
-      <text>
-        <t>Principal sized to hit target DSCR given CFADS. No Goal Seek needed — formula calculates directly.</t>
-      </text>
-    </comment>
-    <comment ref="C81" authorId="0" shapeId="0">
-      <text>
-        <t>Debt remaining after payments. Should reach zero by tenor end. MAX(0,...) prevents negative balance.</t>
+        <t>Debt Service Coverage Ratio. Key lender metric. Target: 1.25-1.40x.</t>
       </text>
     </comment>
     <comment ref="C82" authorId="0" shapeId="0">
       <text>
-        <t>Debt Service Coverage Ratio. Key lender metric. &lt;1.0x means insufficient cash to pay debt. Target: 1.25-1.40x.</t>
+        <t>Debt Service Coverage Ratio. Key lender metric. Target: 1.25-1.40x.</t>
       </text>
     </comment>
     <comment ref="C85" authorId="0" shapeId="0">
       <text>
-        <t>Reserve sized to cover NEXT years debt service. Uses SCHEDULED DS (not actual) to avoid circular reference. Released at exit.</t>
-      </text>
-    </comment>
-    <comment ref="C87" authorId="0" shapeId="0">
-      <text>
-        <t>Positive = funding requirement (reduces distributable). Negative = release (increases distributable).</t>
-      </text>
-    </comment>
-    <comment ref="C93" authorId="0" shapeId="0">
-      <text>
-        <t>Cash available to equity after debt service and DSRA. Trapped if DSCR below lock-up threshold.</t>
-      </text>
-    </comment>
-    <comment ref="C98" authorId="0" shapeId="0">
-      <text>
-        <t>Typical 1-2% of EV for legal, accounting, advisory fees. Funded at close, increases total uses.</t>
-      </text>
-    </comment>
-    <comment ref="C99" authorId="0" shapeId="0">
-      <text>
-        <t>Positive = funding requirement (reduces distributable). Negative = release (increases distributable).</t>
-      </text>
-    </comment>
-    <comment ref="C104" authorId="0" shapeId="0">
-      <text>
-        <t>30% ITC reduces equity basis at close. Net Equity = Gross − (EV × ITC%). Significantly improves IRR.</t>
-      </text>
-    </comment>
-    <comment ref="C105" authorId="0" shapeId="0">
-      <text>
-        <t>30% ITC reduces equity basis at close. Net Equity = Gross − (EV × ITC%). Significantly improves IRR.</t>
+        <t>Reserve sized to cover NEXT years debt service. Uses SCHEDULED DS to avoid circular reference.</t>
       </text>
     </comment>
     <comment ref="C118" authorId="0" shapeId="0">
       <text>
-        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra).</t>
       </text>
     </comment>
     <comment ref="C119" authorId="0" shapeId="0">
       <text>
-        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money. Less sensitive to timing than IRR.</t>
+        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money.</t>
       </text>
     </comment>
     <comment ref="C123" authorId="0" shapeId="0">
       <text>
-        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra). Leverage amplifies returns.</t>
+        <t>Return to equity after debt service. Should exceed cost of equity (12-15% for infra).</t>
       </text>
     </comment>
   </commentList>
@@ -773,7 +603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N123"/>
+  <dimension ref="A1:N159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -884,9 +714,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C4" s="6">
-        <f> Revenue − OpEx</f>
-        <v/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Revenue minus OpEx</t>
+        </is>
       </c>
       <c r="D4" s="7">
         <f>E68</f>
@@ -904,9 +735,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C5" s="6">
-        <f> EBITDA − Taxes</f>
-        <v/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA minus Taxes</t>
+        </is>
       </c>
       <c r="D5" s="7">
         <f>AVERAGE(E73:N73)</f>
@@ -924,9 +756,10 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C6" s="6">
-        <f> CFADS / Debt Service</f>
-        <v/>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>CFADS / Debt Service</t>
+        </is>
       </c>
       <c r="D6" s="21">
         <f>MIN(E82:N82)</f>
@@ -944,9 +777,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C7" s="6">
-        <f> IRR(Equity CF)</f>
-        <v/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
       </c>
       <c r="D7" s="22">
         <f>D118</f>
@@ -964,9 +798,10 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C8" s="6">
-        <f> Total In / Total Out</f>
-        <v/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Total In / Total Out</t>
+        </is>
       </c>
       <c r="D8" s="21">
         <f>D119</f>
@@ -984,9 +819,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C9" s="6">
-        <f> IRR(Equity CF)</f>
-        <v/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
       </c>
       <c r="D9" s="22">
         <f>D123</f>
@@ -1046,15 +882,18 @@
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr"/>
-      <c r="C13" s="6">
-        <f> CFADS / Debt Service</f>
-        <v/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>CFADS / Debt Service</t>
+        </is>
       </c>
       <c r="D13" s="10">
         <f>IF(D6&gt;=1.30,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
+    <row r="14"/>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -1175,6 +1014,7 @@
         <v>10</v>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
@@ -1255,6 +1095,7 @@
         <v>0.005</v>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
@@ -1355,6 +1196,7 @@
         <v>0.02</v>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
@@ -1455,6 +1297,7 @@
         <v>5</v>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
@@ -1595,6 +1438,7 @@
         <v>1.1</v>
       </c>
     </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
@@ -1675,6 +1519,7 @@
         <v>0.15</v>
       </c>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
@@ -1758,6 +1603,7 @@
         <v/>
       </c>
     </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
@@ -1848,7 +1694,7 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>$/MWh contracted price</t>
+          <t>Escalated</t>
         </is>
       </c>
       <c r="E60" s="16">
@@ -1892,6 +1738,7 @@
         <v/>
       </c>
     </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
@@ -2059,6 +1906,7 @@
         <v/>
       </c>
     </row>
+    <row r="65"/>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
@@ -2116,6 +1964,7 @@
         <v/>
       </c>
     </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
@@ -2127,9 +1976,10 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C68" s="6">
-        <f> Revenue − OpEx</f>
-        <v/>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Revenue minus OpEx</t>
+        </is>
       </c>
       <c r="E68" s="7">
         <f>E64-E66</f>
@@ -2172,6 +2022,7 @@
         <v/>
       </c>
     </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
@@ -2363,6 +2214,7 @@
         <v/>
       </c>
     </row>
+    <row r="74"/>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
@@ -2370,9 +2222,10 @@
         </is>
       </c>
       <c r="B75" s="4" t="n"/>
-      <c r="C75" s="4">
-        <f> CFADS / Debt Service</f>
-        <v/>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>CFADS / Debt Service</t>
+        </is>
       </c>
       <c r="D75" s="4" t="n"/>
       <c r="E75" s="4" t="n"/>
@@ -2397,10 +2250,7 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C76" s="6">
-        <f> Prior Yr End Bal</f>
-        <v/>
-      </c>
+      <c r="C76" s="6" t="inlineStr"/>
       <c r="E76" s="16">
         <f>$D$55</f>
         <v/>
@@ -2784,6 +2634,7 @@
         <v/>
       </c>
     </row>
+    <row r="83"/>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
@@ -3044,6 +2895,7 @@
         <v/>
       </c>
     </row>
+    <row r="89"/>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
@@ -3231,6 +3083,7 @@
         <v/>
       </c>
     </row>
+    <row r="94"/>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
@@ -3288,11 +3141,7 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>% of EV for legal, advisory</t>
-        </is>
-      </c>
+      <c r="C98" s="6" t="inlineStr"/>
       <c r="D98" s="16">
         <f>$D$17*$D$18</f>
         <v/>
@@ -3309,10 +3158,7 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C99" s="6">
-        <f> Target − Beginning</f>
-        <v/>
-      </c>
+      <c r="C99" s="6" t="inlineStr"/>
       <c r="D99" s="16">
         <f>D85</f>
         <v/>
@@ -3335,6 +3181,7 @@
         <v/>
       </c>
     </row>
+    <row r="101"/>
     <row r="102">
       <c r="A102" s="20" t="inlineStr">
         <is>
@@ -3454,6 +3301,7 @@
         <v/>
       </c>
     </row>
+    <row r="109"/>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
@@ -3558,6 +3406,7 @@
         <v/>
       </c>
     </row>
+    <row r="115"/>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
@@ -3646,9 +3495,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C118" s="6">
-        <f> IRR(Equity CF)</f>
-        <v/>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
       </c>
       <c r="D118" s="22">
         <f>IRR(D117:N117)</f>
@@ -3676,6 +3526,7 @@
         <v/>
       </c>
     </row>
+    <row r="120"/>
     <row r="121">
       <c r="A121" s="20" t="inlineStr">
         <is>
@@ -3753,207 +3604,54 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C123" s="6">
-        <f> IRR(Equity CF)</f>
-        <v/>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
       </c>
       <c r="D123" s="22">
         <f>IRR(D122:N122)</f>
         <v/>
       </c>
     </row>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="25" t="inlineStr">
-        <is>
-          <t>INVESTMENT COMMITTEE MEMORANDUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Utility-Scale Solar + BESS Project</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
-        <is>
-          <t>EXECUTIVE SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
-        <is>
-          <t>• Acquire 150 MW solar + 50 MW/200 MWh BESS at $280mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="27" t="inlineStr">
-        <is>
-          <t>• 20-year PPA with investment-grade offtaker at $55/MWh</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="27" t="inlineStr">
-        <is>
-          <t>• Contracted cash flows enable sculpted debt structure</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="27" t="inlineStr">
-        <is>
-          <t>• Target returns: 10-12% levered IRR, 1.6-1.8x MOIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1"/>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="26" t="inlineStr">
-        <is>
-          <t>INVESTMENT THESIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>1. Long-term contracted revenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   20-year PPA eliminates merchant risk. Creditworthy offtaker provides revenue certainty.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="28" t="inlineStr">
-        <is>
-          <t>2. ITC benefit enhances returns</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   30% Investment Tax Credit reduces equity basis, significantly improving IRR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="28" t="inlineStr">
-        <is>
-          <t>3. Storage adds value stack</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   BESS enables arbitrage, ancillary services, and capacity revenue beyond solar-only project.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1"/>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="26" t="inlineStr">
-        <is>
-          <t>KEY RISKS &amp; MITIGANTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="28" t="inlineStr">
-        <is>
-          <t>Risk | Mitigant</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="27" t="inlineStr">
-        <is>
-          <t>Panel degradation | Tier-1 modules with performance guarantees; conservative degradation assumptions</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="27" t="inlineStr">
-        <is>
-          <t>Battery degradation | Augmentation capex budgeted for Year 5-7</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="27" t="inlineStr">
-        <is>
-          <t>Curtailment risk | PPAincludes curtailment provisions; transmission study completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1"/>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="26" t="inlineStr">
-        <is>
-          <t>FINANCIAL SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="27" t="inlineStr">
-        <is>
-          <t>Entry EV: $280mm | Leverage: 65% | Min DSCR: 1.35x</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="27" t="inlineStr">
-        <is>
-          <t>Levered IRR: 11.0% | MOIC: 1.7x</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1"/>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="26" t="inlineStr">
-        <is>
-          <t>RECOMMENDATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="27" t="inlineStr">
-        <is>
-          <t>Recommend APPROVAL subject to satisfactory completion of confirmatory due diligence.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/deliverables/deliverables-20260120-0030/Model_3_SolarBESS.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_3_SolarBESS.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
     <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,6 +52,25 @@
     <font>
       <b val="1"/>
       <color rgb="000000FF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -103,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -133,6 +153,18 @@
     <xf numFmtId="166" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -603,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N159"/>
+  <dimension ref="A1:N123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -892,8 +924,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -1014,7 +1044,6 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
@@ -1095,7 +1124,6 @@
         <v>0.005</v>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
@@ -1196,7 +1224,6 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
@@ -1297,7 +1324,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
@@ -1438,7 +1464,6 @@
         <v>1.1</v>
       </c>
     </row>
-    <row r="47"/>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
@@ -1519,7 +1544,6 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
@@ -1603,7 +1627,6 @@
         <v/>
       </c>
     </row>
-    <row r="57"/>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
@@ -1738,7 +1761,6 @@
         <v/>
       </c>
     </row>
-    <row r="61"/>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
@@ -1906,7 +1928,6 @@
         <v/>
       </c>
     </row>
-    <row r="65"/>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
@@ -1964,7 +1985,6 @@
         <v/>
       </c>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
@@ -2022,7 +2042,6 @@
         <v/>
       </c>
     </row>
-    <row r="69"/>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
@@ -2214,7 +2233,6 @@
         <v/>
       </c>
     </row>
-    <row r="74"/>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
@@ -2634,7 +2652,6 @@
         <v/>
       </c>
     </row>
-    <row r="83"/>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
@@ -2895,7 +2912,6 @@
         <v/>
       </c>
     </row>
-    <row r="89"/>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
@@ -3083,7 +3099,6 @@
         <v/>
       </c>
     </row>
-    <row r="94"/>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
@@ -3181,7 +3196,6 @@
         <v/>
       </c>
     </row>
-    <row r="101"/>
     <row r="102">
       <c r="A102" s="20" t="inlineStr">
         <is>
@@ -3301,7 +3315,6 @@
         <v/>
       </c>
     </row>
-    <row r="109"/>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
@@ -3406,7 +3419,6 @@
         <v/>
       </c>
     </row>
-    <row r="115"/>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
@@ -3526,7 +3538,6 @@
         <v/>
       </c>
     </row>
-    <row r="120"/>
     <row r="121">
       <c r="A121" s="20" t="inlineStr">
         <is>
@@ -3614,44 +3625,269 @@
         <v/>
       </c>
     </row>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>PROJECT SUNVAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>INVESTMENT COMMITTEE MEMORANDUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>115 MWac Solar + 50 MW/200 MWh BESS – ERCOT West</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>RECOMMENDATION: Proceed to final bid at $145mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>KEY METRICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>• 10-year investment-grade PPA provides contracted revenue certainty, supporting sculpted debt structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>• 30% ITC reduces equity requirement by $43.5mm, significantly enhancing returns</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>• BESS provides additional revenue streams (arbitrage, ancillary) with limited incremental risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>• Exit to yield-oriented infrastructure buyer at premium multiple (8.0x vs 6.5x for thermal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>KEY RISKS &amp; MITIGANTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>ANTICIPATED IC Q&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>Q: Why sculpted debt instead of sweep?</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>A: Contracted PPA provides predictable CFADS. Sculpting efficiently sizes debt service to maintain target DSCR, maximizing debt capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>Q: How does ITC flow through S&amp;U?</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>A: ITC is a "source" offsetting equity. Pre-ITC Equity ($98mm) - ITC ($43.5mm) = Net Equity ($55mm). You write a $55mm check, not $98mm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>Q: What happens to BESS revenue if volatility drops?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>A: Arbitrage revenue declines but ancillary services (frequency regulation) remain stable. PPA revenue is 80% of total – BESS is upside.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>Q: Why Y7 augmentation capex?</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>A: Battery capacity degrades 2-3% annually. Y7 augmentation ($5mm) restores capacity to maintain contracted services. Factor into CFADS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>Metric | Base Case | Downside | Upside</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>Entry EV | $145mm | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
+          <t>Entry Multiple | 9.2x Y1 EBITDA | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>Leverage | 35% | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t>Net Equity (post-ITC) | $55mm | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
+          <t>Levered IRR | 17.2% | 13.8% | 20.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="28" t="inlineStr">
+        <is>
+          <t>MOIC | 2.35x | 2.05x | 2.65x</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="28" t="inlineStr">
+        <is>
+          <t>Min DSCR | 1.35x | 1.28x | 1.42x</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="25" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>Risk | Probability | Mitigant</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>Degradation exceeds forecast | Low | Panel warranty covers 80% output at Y25; 0.5%/yr is conservative</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>BESS revenue volatility | Medium | BESS = 20% of revenue; PPA provides floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>Offtaker credit risk | Low | Investment-grade utility; standard security package</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>ITC recapture | Low | 5-year recapture period; no change of control planned</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/deliverables/deliverables-20260120-0030/Model_3_SolarBESS.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_3_SolarBESS.xlsx
@@ -7,8 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Prompt" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,7 @@
     <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,6 +73,9 @@
     <font>
       <name val="Consolas"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -123,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -165,6 +170,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -635,6 +641,427 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SolarBESS - INTUITION MAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>WHAT THIS MODEL DOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Solar + Battery - Contracted PPA with merchant upside.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>KEY VALUE DRIVERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1. PPA Price</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2. Degradation</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3. Battery Cycling</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>DEBT STRUCTURE RATIONALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sculpted 1.35x - contracted cash flows.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CASE STUDY: SolarBESS ACQUISITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Time: 4 hours | Deliverables: Model + IC Memo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>SITUATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>150 MW solar + 75MW BESS in ERCOT at $280mm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>KEY QUESTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1. What levered IRR at indicative price?</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2. Downside DSCR under stress?</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3. Key diligence items?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4. Protections to negotiate?</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>PROJECT SUNVAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>INVESTMENT COMMITTEE MEMORANDUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>115 MWac Solar + 50 MW/200 MWh BESS – ERCOT West</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>RECOMMENDATION: Proceed to final bid at $145mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>────────────────────────────────────────────────────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>KEY METRICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>• 10-year investment-grade PPA provides contracted revenue certainty, supporting sculpted debt structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>• 30% ITC reduces equity requirement by $43.5mm, significantly enhancing returns</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>• BESS provides additional revenue streams (arbitrage, ancillary) with limited incremental risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>• Exit to yield-oriented infrastructure buyer at premium multiple (8.0x vs 6.5x for thermal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>KEY RISKS &amp; MITIGANTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>ANTICIPATED IC Q&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>Q: Why sculpted debt instead of sweep?</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>A: Contracted PPA provides predictable CFADS. Sculpting efficiently sizes debt service to maintain target DSCR, maximizing debt capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>Q: How does ITC flow through S&amp;U?</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>A: ITC is a "source" offsetting equity. Pre-ITC Equity ($98mm) - ITC ($43.5mm) = Net Equity ($55mm). You write a $55mm check, not $98mm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>Q: What happens to BESS revenue if volatility drops?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>A: Arbitrage revenue declines but ancillary services (frequency regulation) remain stable. PPA revenue is 80% of total – BESS is upside.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>Q: Why Y7 augmentation capex?</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>A: Battery capacity degrades 2-3% annually. Y7 augmentation ($5mm) restores capacity to maintain contracted services. Factor into CFADS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>Metric | Base Case | Downside | Upside</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>Entry EV | $145mm | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
+          <t>Entry Multiple | 9.2x Y1 EBITDA | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>Leverage | 35% | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t>Net Equity (post-ITC) | $55mm | - | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
+          <t>Levered IRR | 17.2% | 13.8% | 20.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="28" t="inlineStr">
+        <is>
+          <t>MOIC | 2.35x | 2.05x | 2.65x</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="28" t="inlineStr">
+        <is>
+          <t>Min DSCR | 1.35x | 1.28x | 1.42x</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="25" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>Risk | Probability | Mitigant</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>Degradation exceeds forecast | Low | Panel warranty covers 80% output at Y25; 0.5%/yr is conservative</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>BESS revenue volatility | Medium | BESS = 20% of revenue; PPA provides floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>Offtaker credit risk | Low | Investment-grade utility; standard security package</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>ITC recapture | Low | 5-year recapture period; no change of control planned</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -794,7 +1221,7 @@
         </is>
       </c>
       <c r="D6" s="21">
-        <f>MIN(E82:N82)</f>
+        <f>IF(COUNTIF(E82:N82,"&gt;0")&gt;0,MINIFS(E82:N82,E82:N82,"&gt;0"),0)</f>
         <v/>
       </c>
     </row>
@@ -3629,265 +4056,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="25" t="inlineStr">
-        <is>
-          <t>PROJECT SUNVAULT</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="26" t="inlineStr">
-        <is>
-          <t>INVESTMENT COMMITTEE MEMORANDUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="25" t="inlineStr">
-        <is>
-          <t>115 MWac Solar + 50 MW/200 MWh BESS – ERCOT West</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="26" t="inlineStr">
-        <is>
-          <t>RECOMMENDATION: Proceed to final bid at $145mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="25" t="inlineStr">
-        <is>
-          <t>────────────────────────────────────────────────────────────</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="26" t="inlineStr">
-        <is>
-          <t>KEY METRICS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="26" t="inlineStr">
-        <is>
-          <t>INVESTMENT THESIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="25" t="inlineStr">
-        <is>
-          <t>• 10-year investment-grade PPA provides contracted revenue certainty, supporting sculpted debt structure</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="25" t="inlineStr">
-        <is>
-          <t>• 30% ITC reduces equity requirement by $43.5mm, significantly enhancing returns</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="25" t="inlineStr">
-        <is>
-          <t>• BESS provides additional revenue streams (arbitrage, ancillary) with limited incremental risk</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="25" t="inlineStr">
-        <is>
-          <t>• Exit to yield-oriented infrastructure buyer at premium multiple (8.0x vs 6.5x for thermal)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>KEY RISKS &amp; MITIGANTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="26" t="inlineStr">
-        <is>
-          <t>ANTICIPATED IC Q&amp;A</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="26" t="inlineStr">
-        <is>
-          <t>Q: Why sculpted debt instead of sweep?</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="25" t="inlineStr">
-        <is>
-          <t>A: Contracted PPA provides predictable CFADS. Sculpting efficiently sizes debt service to maintain target DSCR, maximizing debt capacity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="26" t="inlineStr">
-        <is>
-          <t>Q: How does ITC flow through S&amp;U?</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="25" t="inlineStr">
-        <is>
-          <t>A: ITC is a "source" offsetting equity. Pre-ITC Equity ($98mm) - ITC ($43.5mm) = Net Equity ($55mm). You write a $55mm check, not $98mm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="27" t="inlineStr">
-        <is>
-          <t>Q: What happens to BESS revenue if volatility drops?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="25" t="inlineStr">
-        <is>
-          <t>A: Arbitrage revenue declines but ancillary services (frequency regulation) remain stable. PPA revenue is 80% of total – BESS is upside.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="26" t="inlineStr">
-        <is>
-          <t>Q: Why Y7 augmentation capex?</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>A: Battery capacity degrades 2-3% annually. Y7 augmentation ($5mm) restores capacity to maintain contracted services. Factor into CFADS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="25" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>Metric | Base Case | Downside | Upside</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>Entry EV | $145mm | - | -</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>Entry Multiple | 9.2x Y1 EBITDA | - | -</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="28" t="inlineStr">
-        <is>
-          <t>Leverage | 35% | - | -</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="28" t="inlineStr">
-        <is>
-          <t>Net Equity (post-ITC) | $55mm | - | -</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="28" t="inlineStr">
-        <is>
-          <t>Levered IRR | 17.2% | 13.8% | 20.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="28" t="inlineStr">
-        <is>
-          <t>MOIC | 2.35x | 2.05x | 2.65x</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="28" t="inlineStr">
-        <is>
-          <t>Min DSCR | 1.35x | 1.28x | 1.42x</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="25" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="28" t="inlineStr">
-        <is>
-          <t>Risk | Probability | Mitigant</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="28" t="inlineStr">
-        <is>
-          <t>Degradation exceeds forecast | Low | Panel warranty covers 80% output at Y25; 0.5%/yr is conservative</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="28" t="inlineStr">
-        <is>
-          <t>BESS revenue volatility | Medium | BESS = 20% of revenue; PPA provides floor</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="28" t="inlineStr">
-        <is>
-          <t>Offtaker credit risk | Low | Investment-grade utility; standard security package</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="28" t="inlineStr">
-        <is>
-          <t>ITC recapture | Low | 5-year recapture period; no change of control planned</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/deliverables/deliverables-20260120-0030/Model_3_SolarBESS.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_3_SolarBESS.xlsx
@@ -2355,6 +2355,7 @@
         <v/>
       </c>
     </row>
+    <row r="65"/>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
@@ -2412,6 +2413,7 @@
         <v/>
       </c>
     </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
@@ -2469,6 +2471,7 @@
         <v/>
       </c>
     </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
@@ -2506,43 +2509,43 @@
         </is>
       </c>
       <c r="E71" s="16">
-        <f>IF(1&lt;=$D$50,0,E68*$D$51)</f>
+        <f>IF(1&lt;=$D$50,0,MAX(0,E68)*$D$51)</f>
         <v/>
       </c>
       <c r="F71" s="16">
-        <f>IF(2&lt;=$D$50,0,F68*$D$51)</f>
+        <f>IF(2&lt;=$D$50,0,MAX(0,F68)*$D$51)</f>
         <v/>
       </c>
       <c r="G71" s="16">
-        <f>IF(3&lt;=$D$50,0,G68*$D$51)</f>
+        <f>IF(3&lt;=$D$50,0,MAX(0,G68)*$D$51)</f>
         <v/>
       </c>
       <c r="H71" s="16">
-        <f>IF(4&lt;=$D$50,0,H68*$D$51)</f>
+        <f>IF(4&lt;=$D$50,0,MAX(0,H68)*$D$51)</f>
         <v/>
       </c>
       <c r="I71" s="16">
-        <f>IF(5&lt;=$D$50,0,I68*$D$51)</f>
+        <f>IF(5&lt;=$D$50,0,MAX(0,I68)*$D$51)</f>
         <v/>
       </c>
       <c r="J71" s="16">
-        <f>IF(6&lt;=$D$50,0,J68*$D$51)</f>
+        <f>IF(6&lt;=$D$50,0,MAX(0,J68)*$D$51)</f>
         <v/>
       </c>
       <c r="K71" s="16">
-        <f>IF(7&lt;=$D$50,0,K68*$D$51)</f>
+        <f>IF(7&lt;=$D$50,0,MAX(0,K68)*$D$51)</f>
         <v/>
       </c>
       <c r="L71" s="16">
-        <f>IF(8&lt;=$D$50,0,L68*$D$51)</f>
+        <f>IF(8&lt;=$D$50,0,MAX(0,L68)*$D$51)</f>
         <v/>
       </c>
       <c r="M71" s="16">
-        <f>IF(9&lt;=$D$50,0,M68*$D$51)</f>
+        <f>IF(9&lt;=$D$50,0,MAX(0,M68)*$D$51)</f>
         <v/>
       </c>
       <c r="N71" s="16">
-        <f>IF(10&lt;=$D$50,0,N68*$D$51)</f>
+        <f>IF(10&lt;=$D$50,0,MAX(0,N68)*$D$51)</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Model_3_SolarBESS.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_3_SolarBESS.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,6 +77,10 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="000066CC"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -128,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -171,6 +175,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -641,72 +652,627 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SolarBESS - INTUITION MAP</t>
+      <c r="A1">
+        <f>==========================================================================</f>
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>LOTUS INFRASTRUCTURE PARTNERS</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="29" t="inlineStr">
-        <is>
-          <t>WHAT THIS MODEL DOES</t>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>CASE STUDY: SOLAR PV + BATTERY ENERGY STORAGE ACQUISITION</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Solar + Battery - Contracted PPA with merchant upside.</t>
-        </is>
+      <c r="A4">
+        <f>==========================================================================</f>
+        <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>KEY VALUE DRIVERS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1. PPA Price</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TIME: 4 Hours | DATE: January 2026 | DELIVERABLES: Model + IC Memo</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2. Degradation</t>
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>--- MODEL TIMELINE ---</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3. Battery Cycling</t>
+          <t>Year 0 (2025): Transaction close Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Year 1 (2026): First full year; PPA Year 3</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="inlineStr">
-        <is>
-          <t>DEBT STRUCTURE RATIONALE</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Year 13 (2038): PPA expiration; merchant transition</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sculpted 1.35x - contracted cash flows.</t>
+          <t>Year 15 (2040): End of typical solar asset life</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>--- SITUATION ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>Lotus Infrastructure Partners is evaluating a 150 MW solar PV facility
+with co-located 75 MW / 300 MWh battery storage in ERCOT West zone. The
+project achieved COD in Q1 2024 (operating ~2 years).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>The solar facility has a 15-year fixed-price PPA at $35/MWh with an IG utility
+offtaker (A- rating). Approximately 13 years remain from close. Post-PPA
+revenue depends on merchant market conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>The battery generates revenue through energy arbitrage and ancillary services,
+limited to ~365 cycles/year for warranty preservation. The project received
+30% ITC at COD (already monetized) with MACRS depreciation through Year 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>The seller is asking $280mm with bids due by February 28, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>--- KEY VALUE DRIVERS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>* PPA Price/Tenor: Contracted revenue at $35/MWh for 13 remaining years</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>* Degradation: 0.5%/year panel efficiency loss - compounds over time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>* Battery Cycling: 365 cycles/year limit; affects arbitrage opportunity</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>* Post-PPA Merchant: Tail value uncertain; conservative assumptions key</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="29" t="inlineStr">
+        <is>
+          <t>--- STEP-BY-STEP MODEL BUILDING GUIDE ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="inlineStr">
+        <is>
+          <t>STEP-BY-STEP MODEL BUILDING GUIDE FOR SOLAR+BESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>KEY DIFFERENCES:</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>- NO fuel cost - margins effectively 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="31" t="inlineStr">
+        <is>
+          <t>- Degradation reduces output each year (compounds!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="31" t="inlineStr">
+        <is>
+          <t>- PPA provides contracted revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="31" t="inlineStr">
+        <is>
+          <t>- Tax treatment: ITC taken, MACRS shield through Y6</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="31" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="31" t="inlineStr">
+        <is>
+          <t>1. SET UP INPUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Solar Capacity: 150 MW</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Capacity Factor: 25-28%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Degradation: 0.5%/year (COMPOUNDS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - PPA Price: $35/MWh (fixed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - PPA Tenor: 13 years remaining</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Post-PPA Price: Conservative merchant</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="31" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="31" t="inlineStr">
+        <is>
+          <t>2. BUILD GENERATION WITH DEGRADATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Year 1 Generation = Capacity x CF x 8760</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Year n Generation = Year 1 x (1 - Degradation)^(n-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Example: Y10 = Y1 x 0.995^9 = ~95.6% of Y1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="31" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="31" t="inlineStr">
+        <is>
+          <t>3. BUILD TAX SCHEDULE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Years 1-6: MACRS shield = ZERO taxes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Years 7+: Normal taxation</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Formula: =IF(Year &lt;= Shield_Years, 0, MAX(0, EBIT) x Rate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="31" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="31" t="inlineStr">
+        <is>
+          <t>4. SCULPTED DEBT (NOT Cash Sweep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Solar+BESS with PPA uses SCULPTED debt:</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Cash flows predictable (contracted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Lenders comfortable with 1.30-1.40x DSCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Sculpted Principal = MIN(MAX(0, CFADS/Target_DSCR - Interest), Beg_Bal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="29" t="inlineStr">
+        <is>
+          <t>--- HOW TO AVOID CIRCULARITY ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SCULPTED DEBT - NO CIRCULARITY ISSUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unlike cash sweep, sculpted debt is calculated FROM CFADS:</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1. Know CFADS (revenue - opex - taxes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2. Calculate Target DS = CFADS / Target DSCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>3. Calculate Principal = Target DS - Interest</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>4. DSRA Target references this known DS</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>No circular loop because everything flows from CFADS downward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="29" t="inlineStr">
+        <is>
+          <t>--- ALTERNATIVE SCENARIOS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ALTERNATIVE SCENARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>A. Tax Equity Partnership:</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - If ITC not yet monetized</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Complex waterfall with flip date</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>B. Merchant Solar (No PPA):</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Much riskier - lower leverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - May not be financeable with project debt</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>C. Standalone BESS:</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - No solar, just storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Revenue from pure arbitrage</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="29" t="inlineStr">
+        <is>
+          <t>--- QA CHECKS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>QA CHECKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1. Degradation compounds correctly (Y10 &lt; 95% of Y1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2. Tax is $0 for MACRS shield years</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>3. Tax formula has MAX(0,...) guardrail</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>4. PPA revenue switches to merchant at correct year</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>5. DSCR is ~1.30-1.40x (sculpted to target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="29" t="inlineStr">
+        <is>
+          <t>--- HINTS &amp; PITFALLS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="32" t="inlineStr">
+        <is>
+          <t>* Degradation at 0.5%/yr means Y10 is ~95.6% of Y1 (not 95%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="32" t="inlineStr">
+        <is>
+          <t>* ITC already taken - no tax equity modeling needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="32" t="inlineStr">
+        <is>
+          <t>* Post-PPA price should be conservative (70-80% of PPA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="32" t="inlineStr">
+        <is>
+          <t>* MACRS shield means ~6 years of zero taxes</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="29" t="inlineStr">
+        <is>
+          <t>--- INTERVIEW QUESTIONS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Q: How does 0.5% vs 0.7% annual degradation affect exit value?</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Q: What's your post-PPA merchant assumption and why?</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Q: Why use sculpted debt instead of cash sweep?</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Q: What would make you walk away from this deal?</t>
         </is>
       </c>
     </row>
@@ -1087,38 +1653,60 @@
           <t>Solar+BESS Model - Lotus Infrastructure Partners</t>
         </is>
       </c>
-      <c r="D1" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I1" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J1" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K1" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L1" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M1" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="N1" s="2" t="n">
-        <v>10</v>
+      <c r="D1" s="30" t="inlineStr">
+        <is>
+          <t>Y0 (2025)</t>
+        </is>
+      </c>
+      <c r="E1" s="30" t="inlineStr">
+        <is>
+          <t>Y1 (2026)</t>
+        </is>
+      </c>
+      <c r="F1" s="30" t="inlineStr">
+        <is>
+          <t>Y2 (2027)</t>
+        </is>
+      </c>
+      <c r="G1" s="30" t="inlineStr">
+        <is>
+          <t>Y3 (2028)</t>
+        </is>
+      </c>
+      <c r="H1" s="30" t="inlineStr">
+        <is>
+          <t>Y4 (2029)</t>
+        </is>
+      </c>
+      <c r="I1" s="30" t="inlineStr">
+        <is>
+          <t>Y5 (2030)</t>
+        </is>
+      </c>
+      <c r="J1" s="30" t="inlineStr">
+        <is>
+          <t>Y6 (2031)</t>
+        </is>
+      </c>
+      <c r="K1" s="30" t="inlineStr">
+        <is>
+          <t>Y7 (2032)</t>
+        </is>
+      </c>
+      <c r="L1" s="30" t="inlineStr">
+        <is>
+          <t>Y8 (2033)</t>
+        </is>
+      </c>
+      <c r="M1" s="30" t="inlineStr">
+        <is>
+          <t>Y9 (2034)</t>
+        </is>
+      </c>
+      <c r="N1" s="30" t="inlineStr">
+        <is>
+          <t>Y10 (2035)</t>
+        </is>
       </c>
     </row>
     <row r="2">
@@ -2355,7 +2943,6 @@
         <v/>
       </c>
     </row>
-    <row r="65"/>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
@@ -2413,7 +3000,6 @@
         <v/>
       </c>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
@@ -2471,7 +3057,6 @@
         <v/>
       </c>
     </row>
-    <row r="69"/>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>

--- a/deliverables/deliverables-20260120-0030/Model_3_SolarBESS.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_3_SolarBESS.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -105,6 +105,12 @@
       <color rgb="001F4E79"/>
       <sz val="12"/>
     </font>
+    <font/>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -156,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,6 +223,14 @@
     <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1160,7 +1174,6 @@
         </is>
       </c>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
@@ -1196,7 +1209,6 @@
         </is>
       </c>
     </row>
-    <row r="70"/>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
@@ -1218,7 +1230,6 @@
         </is>
       </c>
     </row>
-    <row r="75"/>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
@@ -1240,7 +1251,6 @@
         </is>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
@@ -1262,7 +1272,6 @@
         </is>
       </c>
     </row>
-    <row r="83"/>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
@@ -1298,7 +1307,6 @@
         </is>
       </c>
     </row>
-    <row r="90"/>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
@@ -1854,7 +1862,6 @@
           <t>4:00</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="36" t="inlineStr">
@@ -3486,216 +3493,196 @@
     <row r="5">
       <c r="A5" s="33" t="inlineStr">
         <is>
-          <t>═══════════════════ CONTROL PANEL ═══════════════════</t>
-        </is>
-      </c>
+          <t>═══════════ CONTROL PANEL ═══════════</t>
+        </is>
+      </c>
+      <c r="B5" s="44" t="n"/>
+      <c r="C5" s="44" t="n"/>
+      <c r="D5" s="44" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="44" t="n"/>
+      <c r="B6" s="44" t="n"/>
+      <c r="C6" s="44" t="n"/>
+      <c r="D6" s="44" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
-        <is>
-          <t>Revenue Mode</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Merchant / Contracted / Hybrid</t>
-        </is>
-      </c>
-      <c r="D7" s="42" t="inlineStr">
-        <is>
-          <t>Merchant</t>
-        </is>
-      </c>
+      <c r="A7" s="45" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+      <c r="B7" s="44" t="n"/>
+      <c r="C7" s="44" t="n"/>
+      <c r="D7" s="44" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
         <is>
-          <t>Contract Years</t>
-        </is>
-      </c>
+          <t>Revenue Mode</t>
+        </is>
+      </c>
+      <c r="B8" s="44" t="n"/>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>If Hybrid: years of contracted revenue</t>
+          <t>Merchant / Contracted / Hybrid</t>
         </is>
       </c>
       <c r="D8" s="42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Merchant</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
         <is>
+          <t>Contract End Year</t>
+        </is>
+      </c>
+      <c r="B9" s="44" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>0 = pure merchant; else year PPA ends</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="44" t="n"/>
+      <c r="B10" s="44" t="n"/>
+      <c r="C10" s="44" t="n"/>
+      <c r="D10" s="44" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="45" t="inlineStr">
+        <is>
+          <t>TIMING</t>
+        </is>
+      </c>
+      <c r="B11" s="44" t="n"/>
+      <c r="C11" s="44" t="n"/>
+      <c r="D11" s="44" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>Exit Year</t>
+        </is>
+      </c>
+      <c r="B12" s="44" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>5 / 7 / 10</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>Tax Credit End Year</t>
+        </is>
+      </c>
+      <c r="B13" s="44" t="n"/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>0 = N/A; else last year of PTC/ITC</t>
+        </is>
+      </c>
+      <c r="D13" s="42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="44" t="n"/>
+      <c r="B14" s="44" t="n"/>
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="44" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="45" t="inlineStr">
+        <is>
+          <t>DEBT</t>
+        </is>
+      </c>
+      <c r="B15" s="44" t="n"/>
+      <c r="C15" s="44" t="n"/>
+      <c r="D15" s="46" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
           <t>Debt Sweep</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>ON / OFF</t>
-        </is>
-      </c>
-      <c r="D9" s="42" t="inlineStr">
+      <c r="B16" s="44" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ON / OFF (for sweep assets)</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>Sweep %</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Only active if Sweep = ON</t>
-        </is>
-      </c>
-      <c r="D10" s="42" t="inlineStr">
+      <c r="B17" s="44" t="n"/>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Active when Sweep = ON</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="44" t="n"/>
+      <c r="B18" s="44" t="n"/>
+      <c r="C18" s="44" t="n"/>
+      <c r="D18" s="47" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="45" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="B19" s="44" t="n"/>
+      <c r="C19" s="44" t="n"/>
+      <c r="D19" s="48" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="49" t="inlineStr">
         <is>
           <t>Exit Method</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="B20" s="44" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Multiple / DCF</t>
         </is>
       </c>
-      <c r="D11" s="42" t="inlineStr">
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>Multiple</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="33" t="inlineStr">
-        <is>
-          <t>════════════════════════════════════════════════════</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Avg CFADS (Y1-Y10)</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>EBITDA minus Taxes</t>
-        </is>
-      </c>
-      <c r="D15" s="7">
-        <f>AVERAGE(E73:N73)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Min DSCR (Y1-Y10)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>CFADS / Debt Service</t>
-        </is>
-      </c>
-      <c r="D16" s="21">
-        <f>IF(COUNTIF(E82:N82,"&gt;0")&gt;0,MINIFS(E82:N82,E82:N82,"&gt;0"),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Levered IRR</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>IRR of Equity CFs</t>
-        </is>
-      </c>
-      <c r="D17" s="22">
-        <f>D118</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Total In / Total Out</t>
-        </is>
-      </c>
-      <c r="D18" s="21">
-        <f>D119</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Unlevered IRR</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>IRR of Equity CFs</t>
-        </is>
-      </c>
-      <c r="D19" s="22">
-        <f>D123</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>═══ QA CHECKS ═══</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
@@ -3708,9 +3695,9 @@
       <c r="N20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>S&amp;U Balance</t>
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>════════════════════════════════════</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr"/>
@@ -3750,8 +3737,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -3872,7 +3857,6 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3937,6 @@
         <v>0.005</v>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
@@ -4054,7 +4037,6 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
@@ -4155,7 +4137,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49"/>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
@@ -4296,7 +4277,6 @@
         <v>1.1</v>
       </c>
     </row>
-    <row r="57"/>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
@@ -4377,7 +4357,6 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="62"/>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
@@ -4461,7 +4440,6 @@
         <v/>
       </c>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
@@ -4596,7 +4574,6 @@
         <v/>
       </c>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
@@ -4764,7 +4741,6 @@
         <v/>
       </c>
     </row>
-    <row r="75"/>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
@@ -4822,7 +4798,6 @@
         <v/>
       </c>
     </row>
-    <row r="77"/>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
@@ -4880,7 +4855,6 @@
         <v/>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
@@ -5072,7 +5046,6 @@
         <v/>
       </c>
     </row>
-    <row r="84"/>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
@@ -5492,7 +5465,6 @@
         <v/>
       </c>
     </row>
-    <row r="93"/>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
@@ -5753,7 +5725,6 @@
         <v/>
       </c>
     </row>
-    <row r="99"/>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
@@ -5941,7 +5912,6 @@
         <v/>
       </c>
     </row>
-    <row r="104"/>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
@@ -6039,7 +6009,6 @@
         <v/>
       </c>
     </row>
-    <row r="111"/>
     <row r="112">
       <c r="A112" s="20" t="inlineStr">
         <is>
@@ -6159,7 +6128,6 @@
         <v/>
       </c>
     </row>
-    <row r="119"/>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
@@ -6264,7 +6232,6 @@
         <v/>
       </c>
     </row>
-    <row r="125"/>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
@@ -6384,7 +6351,6 @@
         <v/>
       </c>
     </row>
-    <row r="130"/>
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
@@ -6641,216 +6607,196 @@
     <row r="5">
       <c r="A5" s="33" t="inlineStr">
         <is>
-          <t>═══════════════════ CONTROL PANEL ═══════════════════</t>
-        </is>
-      </c>
+          <t>═══════════ CONTROL PANEL ═══════════</t>
+        </is>
+      </c>
+      <c r="B5" s="44" t="n"/>
+      <c r="C5" s="44" t="n"/>
+      <c r="D5" s="44" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="44" t="n"/>
+      <c r="B6" s="44" t="n"/>
+      <c r="C6" s="44" t="n"/>
+      <c r="D6" s="44" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
-        <is>
-          <t>Revenue Mode</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Merchant / Contracted / Hybrid</t>
-        </is>
-      </c>
-      <c r="D7" s="42" t="inlineStr">
-        <is>
-          <t>Merchant</t>
-        </is>
-      </c>
+      <c r="A7" s="45" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+      <c r="B7" s="44" t="n"/>
+      <c r="C7" s="44" t="n"/>
+      <c r="D7" s="44" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
         <is>
-          <t>Contract Years</t>
-        </is>
-      </c>
+          <t>Revenue Mode</t>
+        </is>
+      </c>
+      <c r="B8" s="44" t="n"/>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>If Hybrid: years of contracted revenue</t>
+          <t>Merchant / Contracted / Hybrid</t>
         </is>
       </c>
       <c r="D8" s="42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Merchant</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
         <is>
+          <t>Contract End Year</t>
+        </is>
+      </c>
+      <c r="B9" s="44" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>0 = pure merchant; else year PPA ends</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="44" t="n"/>
+      <c r="B10" s="44" t="n"/>
+      <c r="C10" s="44" t="n"/>
+      <c r="D10" s="44" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="45" t="inlineStr">
+        <is>
+          <t>TIMING</t>
+        </is>
+      </c>
+      <c r="B11" s="44" t="n"/>
+      <c r="C11" s="44" t="n"/>
+      <c r="D11" s="44" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>Exit Year</t>
+        </is>
+      </c>
+      <c r="B12" s="44" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>5 / 7 / 10</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>Tax Credit End Year</t>
+        </is>
+      </c>
+      <c r="B13" s="44" t="n"/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>0 = N/A; else last year of PTC/ITC</t>
+        </is>
+      </c>
+      <c r="D13" s="42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="44" t="n"/>
+      <c r="B14" s="44" t="n"/>
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="44" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="45" t="inlineStr">
+        <is>
+          <t>DEBT</t>
+        </is>
+      </c>
+      <c r="B15" s="44" t="n"/>
+      <c r="C15" s="44" t="n"/>
+      <c r="D15" s="46" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
           <t>Debt Sweep</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>ON / OFF</t>
-        </is>
-      </c>
-      <c r="D9" s="42" t="inlineStr">
+      <c r="B16" s="44" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ON / OFF (for sweep assets)</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>Sweep %</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Only active if Sweep = ON</t>
-        </is>
-      </c>
-      <c r="D10" s="42" t="inlineStr">
+      <c r="B17" s="44" t="n"/>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Active when Sweep = ON</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="44" t="n"/>
+      <c r="B18" s="44" t="n"/>
+      <c r="C18" s="44" t="n"/>
+      <c r="D18" s="47" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="45" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="B19" s="44" t="n"/>
+      <c r="C19" s="44" t="n"/>
+      <c r="D19" s="48" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="49" t="inlineStr">
         <is>
           <t>Exit Method</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="B20" s="44" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Multiple / DCF</t>
         </is>
       </c>
-      <c r="D11" s="42" t="inlineStr">
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>Multiple</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="33" t="inlineStr">
-        <is>
-          <t>════════════════════════════════════════════════════</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Avg CFADS (Y1-Y10)</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>EBITDA minus Taxes</t>
-        </is>
-      </c>
-      <c r="D15" s="7">
-        <f>AVERAGE(E73:N73)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Min DSCR (Y1-Y10)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>CFADS / Debt Service</t>
-        </is>
-      </c>
-      <c r="D16" s="21">
-        <f>IF(COUNTIF(E82:N82,"&gt;0")&gt;0,MINIFS(E82:N82,E82:N82,"&gt;0"),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Levered IRR</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>IRR of Equity CFs</t>
-        </is>
-      </c>
-      <c r="D17" s="22">
-        <f>D118</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Total In / Total Out</t>
-        </is>
-      </c>
-      <c r="D18" s="21">
-        <f>D119</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Unlevered IRR</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>IRR of Equity CFs</t>
-        </is>
-      </c>
-      <c r="D19" s="22">
-        <f>D123</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>═══ QA CHECKS ═══</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
@@ -6863,9 +6809,9 @@
       <c r="N20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>S&amp;U Balance</t>
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>════════════════════════════════════</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr"/>
@@ -6905,8 +6851,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -7027,7 +6971,6 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
@@ -7108,7 +7051,6 @@
         <v>0.005</v>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
@@ -7209,7 +7151,6 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
@@ -7310,7 +7251,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49"/>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
@@ -7451,7 +7391,6 @@
         <v>1.1</v>
       </c>
     </row>
-    <row r="57"/>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
@@ -7532,7 +7471,6 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="62"/>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
@@ -7616,7 +7554,6 @@
         <v/>
       </c>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
@@ -7751,7 +7688,6 @@
         <v/>
       </c>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
@@ -7919,7 +7855,6 @@
         <v/>
       </c>
     </row>
-    <row r="75"/>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
@@ -7977,7 +7912,6 @@
         <v/>
       </c>
     </row>
-    <row r="77"/>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
@@ -8035,7 +7969,6 @@
         <v/>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
@@ -8227,7 +8160,6 @@
         <v/>
       </c>
     </row>
-    <row r="84"/>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
@@ -8647,7 +8579,6 @@
         <v/>
       </c>
     </row>
-    <row r="93"/>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
@@ -8908,7 +8839,6 @@
         <v/>
       </c>
     </row>
-    <row r="99"/>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
@@ -9096,7 +9026,6 @@
         <v/>
       </c>
     </row>
-    <row r="104"/>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
@@ -9194,7 +9123,6 @@
         <v/>
       </c>
     </row>
-    <row r="111"/>
     <row r="112">
       <c r="A112" s="20" t="inlineStr">
         <is>
@@ -9314,7 +9242,6 @@
         <v/>
       </c>
     </row>
-    <row r="119"/>
     <row r="120">
       <c r="A120" s="33" t="inlineStr">
         <is>
@@ -9475,7 +9402,6 @@
         <v/>
       </c>
     </row>
-    <row r="131"/>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
@@ -9595,7 +9521,6 @@
         <v/>
       </c>
     </row>
-    <row r="136"/>
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>

--- a/deliverables/deliverables-20260120-0030/Model_3_SolarBESS.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_3_SolarBESS.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -111,6 +111,14 @@
       <i val="1"/>
       <color rgb="00666666"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -162,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -231,6 +239,8 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3468,6 +3478,11 @@
         <f>$D$17</f>
         <v/>
       </c>
+      <c r="M3" s="50" t="inlineStr">
+        <is>
+          <t>IRR Sensitivity:</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -3488,6 +3503,11 @@
       <c r="D4" s="7">
         <f>E68</f>
         <v/>
+      </c>
+      <c r="M4" s="51" t="inlineStr">
+        <is>
+          <t>+/- 5% Entry → ~+/- 1% IRR</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3499,6 +3519,11 @@
       <c r="B5" s="44" t="n"/>
       <c r="C5" s="44" t="n"/>
       <c r="D5" s="44" t="n"/>
+      <c r="M5" s="51" t="inlineStr">
+        <is>
+          <t>+/- 0.5x Exit → ~+/- 1.5% IRR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="44" t="n"/>
@@ -3737,6 +3762,8 @@
         <v/>
       </c>
     </row>
+    <row r="24"/>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -3857,6 +3884,7 @@
         <v>10</v>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
@@ -3937,6 +3965,7 @@
         <v>0.005</v>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
@@ -4037,6 +4066,7 @@
         <v>0.02</v>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
@@ -4137,6 +4167,7 @@
         <v>5</v>
       </c>
     </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
@@ -4277,6 +4308,7 @@
         <v>1.1</v>
       </c>
     </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
@@ -4357,6 +4389,7 @@
         <v>0.15</v>
       </c>
     </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
@@ -4440,6 +4473,7 @@
         <v/>
       </c>
     </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
@@ -4574,6 +4608,7 @@
         <v/>
       </c>
     </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
@@ -4741,6 +4776,7 @@
         <v/>
       </c>
     </row>
+    <row r="75"/>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
@@ -4798,6 +4834,7 @@
         <v/>
       </c>
     </row>
+    <row r="77"/>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
@@ -4855,6 +4892,7 @@
         <v/>
       </c>
     </row>
+    <row r="79"/>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
@@ -5046,6 +5084,7 @@
         <v/>
       </c>
     </row>
+    <row r="84"/>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
@@ -5465,6 +5504,7 @@
         <v/>
       </c>
     </row>
+    <row r="93"/>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
@@ -5725,6 +5765,7 @@
         <v/>
       </c>
     </row>
+    <row r="99"/>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
@@ -5912,6 +5953,7 @@
         <v/>
       </c>
     </row>
+    <row r="104"/>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
@@ -6009,6 +6051,7 @@
         <v/>
       </c>
     </row>
+    <row r="111"/>
     <row r="112">
       <c r="A112" s="20" t="inlineStr">
         <is>
@@ -6128,6 +6171,7 @@
         <v/>
       </c>
     </row>
+    <row r="119"/>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
@@ -6232,6 +6276,7 @@
         <v/>
       </c>
     </row>
+    <row r="125"/>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
@@ -6351,6 +6396,7 @@
         <v/>
       </c>
     </row>
+    <row r="130"/>
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>

--- a/deliverables/deliverables-20260120-0030/Model_3_SolarBESS.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_3_SolarBESS.xlsx
@@ -3475,7 +3475,7 @@
         </is>
       </c>
       <c r="D3" s="7">
-        <f>$D$17</f>
+        <f>$D$27</f>
         <v/>
       </c>
       <c r="M3" s="50" t="inlineStr">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="D4" s="7">
-        <f>E68</f>
+        <f>E78</f>
         <v/>
       </c>
       <c r="M4" s="51" t="inlineStr">
@@ -3762,8 +3762,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -3884,7 +3882,6 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
@@ -3965,7 +3962,6 @@
         <v>0.005</v>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
@@ -4066,7 +4062,6 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
@@ -4167,7 +4162,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49"/>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
@@ -4308,7 +4302,6 @@
         <v>1.1</v>
       </c>
     </row>
-    <row r="57"/>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
@@ -4389,7 +4382,6 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="62"/>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
@@ -4427,7 +4419,7 @@
         </is>
       </c>
       <c r="D64" s="15">
-        <f>$D$24*$D$25*8760</f>
+        <f>$D$34*$D$35*8760</f>
         <v/>
       </c>
     </row>
@@ -4448,7 +4440,7 @@
         </is>
       </c>
       <c r="D65" s="16">
-        <f>$D$17*$D$41</f>
+        <f>$D$27*$D$51</f>
         <v/>
       </c>
     </row>
@@ -4469,11 +4461,10 @@
         </is>
       </c>
       <c r="D66" s="16">
-        <f>$D$17*$D$19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67"/>
+        <f>$D$27*$D$29</f>
+        <v/>
+      </c>
+    </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
@@ -4511,43 +4502,43 @@
         </is>
       </c>
       <c r="E69" s="15">
-        <f>$D$54*(1-$D$26)^(1-1)</f>
+        <f>$D$64*(1-$D$36)^(1-1)</f>
         <v/>
       </c>
       <c r="F69" s="15">
-        <f>$D$54*(1-$D$26)^(2-1)</f>
+        <f>$D$64*(1-$D$36)^(2-1)</f>
         <v/>
       </c>
       <c r="G69" s="15">
-        <f>$D$54*(1-$D$26)^(3-1)</f>
+        <f>$D$64*(1-$D$36)^(3-1)</f>
         <v/>
       </c>
       <c r="H69" s="15">
-        <f>$D$54*(1-$D$26)^(4-1)</f>
+        <f>$D$64*(1-$D$36)^(4-1)</f>
         <v/>
       </c>
       <c r="I69" s="15">
-        <f>$D$54*(1-$D$26)^(5-1)</f>
+        <f>$D$64*(1-$D$36)^(5-1)</f>
         <v/>
       </c>
       <c r="J69" s="15">
-        <f>$D$54*(1-$D$26)^(6-1)</f>
+        <f>$D$64*(1-$D$36)^(6-1)</f>
         <v/>
       </c>
       <c r="K69" s="15">
-        <f>$D$54*(1-$D$26)^(7-1)</f>
+        <f>$D$64*(1-$D$36)^(7-1)</f>
         <v/>
       </c>
       <c r="L69" s="15">
-        <f>$D$54*(1-$D$26)^(8-1)</f>
+        <f>$D$64*(1-$D$36)^(8-1)</f>
         <v/>
       </c>
       <c r="M69" s="15">
-        <f>$D$54*(1-$D$26)^(9-1)</f>
+        <f>$D$64*(1-$D$36)^(9-1)</f>
         <v/>
       </c>
       <c r="N69" s="15">
-        <f>$D$54*(1-$D$26)^(10-1)</f>
+        <f>$D$64*(1-$D$36)^(10-1)</f>
         <v/>
       </c>
     </row>
@@ -4568,47 +4559,46 @@
         </is>
       </c>
       <c r="E70" s="16">
-        <f>$D$29*(1+$D$30)^(1-1)</f>
+        <f>$D$39*(1+$D$40)^(1-1)</f>
         <v/>
       </c>
       <c r="F70" s="16">
-        <f>$D$29*(1+$D$30)^(2-1)</f>
+        <f>$D$39*(1+$D$40)^(2-1)</f>
         <v/>
       </c>
       <c r="G70" s="16">
-        <f>$D$29*(1+$D$30)^(3-1)</f>
+        <f>$D$39*(1+$D$40)^(3-1)</f>
         <v/>
       </c>
       <c r="H70" s="16">
-        <f>$D$29*(1+$D$30)^(4-1)</f>
+        <f>$D$39*(1+$D$40)^(4-1)</f>
         <v/>
       </c>
       <c r="I70" s="16">
-        <f>$D$29*(1+$D$30)^(5-1)</f>
+        <f>$D$39*(1+$D$40)^(5-1)</f>
         <v/>
       </c>
       <c r="J70" s="16">
-        <f>$D$29*(1+$D$30)^(6-1)</f>
+        <f>$D$39*(1+$D$40)^(6-1)</f>
         <v/>
       </c>
       <c r="K70" s="16">
-        <f>$D$29*(1+$D$30)^(7-1)</f>
+        <f>$D$39*(1+$D$40)^(7-1)</f>
         <v/>
       </c>
       <c r="L70" s="16">
-        <f>$D$29*(1+$D$30)^(8-1)</f>
+        <f>$D$39*(1+$D$40)^(8-1)</f>
         <v/>
       </c>
       <c r="M70" s="16">
-        <f>$D$29*(1+$D$30)^(9-1)</f>
+        <f>$D$39*(1+$D$40)^(9-1)</f>
         <v/>
       </c>
       <c r="N70" s="16">
-        <f>$D$29*(1+$D$30)^(10-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71"/>
+        <f>$D$39*(1+$D$40)^(10-1)</f>
+        <v/>
+      </c>
+    </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
@@ -4626,43 +4616,43 @@
         </is>
       </c>
       <c r="E72" s="16">
-        <f>E59*E60/1000000</f>
+        <f>E69*E70/1000000</f>
         <v/>
       </c>
       <c r="F72" s="16">
-        <f>F59*F60/1000000</f>
+        <f>F69*F70/1000000</f>
         <v/>
       </c>
       <c r="G72" s="16">
-        <f>G59*G60/1000000</f>
+        <f>G69*G70/1000000</f>
         <v/>
       </c>
       <c r="H72" s="16">
-        <f>H59*H60/1000000</f>
+        <f>H69*H70/1000000</f>
         <v/>
       </c>
       <c r="I72" s="16">
-        <f>I59*I60/1000000</f>
+        <f>I69*I70/1000000</f>
         <v/>
       </c>
       <c r="J72" s="16">
-        <f>J59*J60/1000000</f>
+        <f>J69*J70/1000000</f>
         <v/>
       </c>
       <c r="K72" s="16">
-        <f>K59*K60/1000000</f>
+        <f>K69*K70/1000000</f>
         <v/>
       </c>
       <c r="L72" s="16">
-        <f>L59*L60/1000000</f>
+        <f>L69*L70/1000000</f>
         <v/>
       </c>
       <c r="M72" s="16">
-        <f>M59*M60/1000000</f>
+        <f>M69*M70/1000000</f>
         <v/>
       </c>
       <c r="N72" s="16">
-        <f>N59*N60/1000000</f>
+        <f>N69*N70/1000000</f>
         <v/>
       </c>
     </row>
@@ -4683,43 +4673,43 @@
         </is>
       </c>
       <c r="E73" s="16">
-        <f>$D$31*(1+$D$32)^(1-1)</f>
+        <f>$D$41*(1+$D$42)^(1-1)</f>
         <v/>
       </c>
       <c r="F73" s="16">
-        <f>$D$31*(1+$D$32)^(2-1)</f>
+        <f>$D$41*(1+$D$42)^(2-1)</f>
         <v/>
       </c>
       <c r="G73" s="16">
-        <f>$D$31*(1+$D$32)^(3-1)</f>
+        <f>$D$41*(1+$D$42)^(3-1)</f>
         <v/>
       </c>
       <c r="H73" s="16">
-        <f>$D$31*(1+$D$32)^(4-1)</f>
+        <f>$D$41*(1+$D$42)^(4-1)</f>
         <v/>
       </c>
       <c r="I73" s="16">
-        <f>$D$31*(1+$D$32)^(5-1)</f>
+        <f>$D$41*(1+$D$42)^(5-1)</f>
         <v/>
       </c>
       <c r="J73" s="16">
-        <f>$D$31*(1+$D$32)^(6-1)</f>
+        <f>$D$41*(1+$D$42)^(6-1)</f>
         <v/>
       </c>
       <c r="K73" s="16">
-        <f>$D$31*(1+$D$32)^(7-1)</f>
+        <f>$D$41*(1+$D$42)^(7-1)</f>
         <v/>
       </c>
       <c r="L73" s="16">
-        <f>$D$31*(1+$D$32)^(8-1)</f>
+        <f>$D$41*(1+$D$42)^(8-1)</f>
         <v/>
       </c>
       <c r="M73" s="16">
-        <f>$D$31*(1+$D$32)^(9-1)</f>
+        <f>$D$41*(1+$D$42)^(9-1)</f>
         <v/>
       </c>
       <c r="N73" s="16">
-        <f>$D$31*(1+$D$32)^(10-1)</f>
+        <f>$D$41*(1+$D$42)^(10-1)</f>
         <v/>
       </c>
     </row>
@@ -4736,47 +4726,46 @@
       </c>
       <c r="C74" s="6" t="inlineStr"/>
       <c r="E74" s="17">
-        <f>E62+E63</f>
+        <f>E72+E73</f>
         <v/>
       </c>
       <c r="F74" s="17">
-        <f>F62+F63</f>
+        <f>F72+F73</f>
         <v/>
       </c>
       <c r="G74" s="17">
-        <f>G62+G63</f>
+        <f>G72+G73</f>
         <v/>
       </c>
       <c r="H74" s="17">
-        <f>H62+H63</f>
+        <f>H72+H73</f>
         <v/>
       </c>
       <c r="I74" s="17">
-        <f>I62+I63</f>
+        <f>I72+I73</f>
         <v/>
       </c>
       <c r="J74" s="17">
-        <f>J62+J63</f>
+        <f>J72+J73</f>
         <v/>
       </c>
       <c r="K74" s="17">
-        <f>K62+K63</f>
+        <f>K72+K73</f>
         <v/>
       </c>
       <c r="L74" s="17">
-        <f>L62+L63</f>
+        <f>L72+L73</f>
         <v/>
       </c>
       <c r="M74" s="17">
-        <f>M62+M63</f>
+        <f>M72+M73</f>
         <v/>
       </c>
       <c r="N74" s="17">
-        <f>N62+N63</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75"/>
+        <f>N72+N73</f>
+        <v/>
+      </c>
+    </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
@@ -4794,47 +4783,46 @@
         </is>
       </c>
       <c r="E76" s="16">
-        <f>$D$35*(1+$D$36)^(1-1)</f>
+        <f>$D$45*(1+$D$46)^(1-1)</f>
         <v/>
       </c>
       <c r="F76" s="16">
-        <f>$D$35*(1+$D$36)^(2-1)</f>
+        <f>$D$45*(1+$D$46)^(2-1)</f>
         <v/>
       </c>
       <c r="G76" s="16">
-        <f>$D$35*(1+$D$36)^(3-1)</f>
+        <f>$D$45*(1+$D$46)^(3-1)</f>
         <v/>
       </c>
       <c r="H76" s="16">
-        <f>$D$35*(1+$D$36)^(4-1)</f>
+        <f>$D$45*(1+$D$46)^(4-1)</f>
         <v/>
       </c>
       <c r="I76" s="16">
-        <f>$D$35*(1+$D$36)^(5-1)</f>
+        <f>$D$45*(1+$D$46)^(5-1)</f>
         <v/>
       </c>
       <c r="J76" s="16">
-        <f>$D$35*(1+$D$36)^(6-1)</f>
+        <f>$D$45*(1+$D$46)^(6-1)</f>
         <v/>
       </c>
       <c r="K76" s="16">
-        <f>$D$35*(1+$D$36)^(7-1)</f>
+        <f>$D$45*(1+$D$46)^(7-1)</f>
         <v/>
       </c>
       <c r="L76" s="16">
-        <f>$D$35*(1+$D$36)^(8-1)</f>
+        <f>$D$45*(1+$D$46)^(8-1)</f>
         <v/>
       </c>
       <c r="M76" s="16">
-        <f>$D$35*(1+$D$36)^(9-1)</f>
+        <f>$D$45*(1+$D$46)^(9-1)</f>
         <v/>
       </c>
       <c r="N76" s="16">
-        <f>$D$35*(1+$D$36)^(10-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77"/>
+        <f>$D$45*(1+$D$46)^(10-1)</f>
+        <v/>
+      </c>
+    </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
@@ -4852,47 +4840,46 @@
         </is>
       </c>
       <c r="E78" s="7">
-        <f>E64-E66</f>
+        <f>E74-E76</f>
         <v/>
       </c>
       <c r="F78" s="7">
-        <f>F64-F66</f>
+        <f>F74-F76</f>
         <v/>
       </c>
       <c r="G78" s="7">
-        <f>G64-G66</f>
+        <f>G74-G76</f>
         <v/>
       </c>
       <c r="H78" s="7">
-        <f>H64-H66</f>
+        <f>H74-H76</f>
         <v/>
       </c>
       <c r="I78" s="7">
-        <f>I64-I66</f>
+        <f>I74-I76</f>
         <v/>
       </c>
       <c r="J78" s="7">
-        <f>J64-J66</f>
+        <f>J74-J76</f>
         <v/>
       </c>
       <c r="K78" s="7">
-        <f>K64-K66</f>
+        <f>K74-K76</f>
         <v/>
       </c>
       <c r="L78" s="7">
-        <f>L64-L66</f>
+        <f>L74-L76</f>
         <v/>
       </c>
       <c r="M78" s="7">
-        <f>M64-M66</f>
+        <f>M74-M76</f>
         <v/>
       </c>
       <c r="N78" s="7">
-        <f>N64-N66</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79"/>
+        <f>N74-N76</f>
+        <v/>
+      </c>
+    </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
@@ -4930,43 +4917,43 @@
         </is>
       </c>
       <c r="E81" s="16">
-        <f>IF(1&lt;=$D$50,0,MAX(0,E68)*$D$51)</f>
+        <f>IF(1&lt;=$D$60,0,MAX(0,E78)*$D$61)</f>
         <v/>
       </c>
       <c r="F81" s="16">
-        <f>IF(2&lt;=$D$50,0,MAX(0,F68)*$D$51)</f>
+        <f>IF(2&lt;=$D$60,0,MAX(0,F78)*$D$61)</f>
         <v/>
       </c>
       <c r="G81" s="16">
-        <f>IF(3&lt;=$D$50,0,MAX(0,G68)*$D$51)</f>
+        <f>IF(3&lt;=$D$60,0,MAX(0,G78)*$D$61)</f>
         <v/>
       </c>
       <c r="H81" s="16">
-        <f>IF(4&lt;=$D$50,0,MAX(0,H68)*$D$51)</f>
+        <f>IF(4&lt;=$D$60,0,MAX(0,H78)*$D$61)</f>
         <v/>
       </c>
       <c r="I81" s="16">
-        <f>IF(5&lt;=$D$50,0,MAX(0,I68)*$D$51)</f>
+        <f>IF(5&lt;=$D$60,0,MAX(0,I78)*$D$61)</f>
         <v/>
       </c>
       <c r="J81" s="16">
-        <f>IF(6&lt;=$D$50,0,MAX(0,J68)*$D$51)</f>
+        <f>IF(6&lt;=$D$60,0,MAX(0,J78)*$D$61)</f>
         <v/>
       </c>
       <c r="K81" s="16">
-        <f>IF(7&lt;=$D$50,0,MAX(0,K68)*$D$51)</f>
+        <f>IF(7&lt;=$D$60,0,MAX(0,K78)*$D$61)</f>
         <v/>
       </c>
       <c r="L81" s="16">
-        <f>IF(8&lt;=$D$50,0,MAX(0,L68)*$D$51)</f>
+        <f>IF(8&lt;=$D$60,0,MAX(0,L78)*$D$61)</f>
         <v/>
       </c>
       <c r="M81" s="16">
-        <f>IF(9&lt;=$D$50,0,MAX(0,M68)*$D$51)</f>
+        <f>IF(9&lt;=$D$60,0,MAX(0,M78)*$D$61)</f>
         <v/>
       </c>
       <c r="N81" s="16">
-        <f>IF(10&lt;=$D$50,0,MAX(0,N68)*$D$51)</f>
+        <f>IF(10&lt;=$D$60,0,MAX(0,N78)*$D$61)</f>
         <v/>
       </c>
     </row>
@@ -4987,43 +4974,43 @@
         </is>
       </c>
       <c r="E82" s="18">
-        <f>IF(1=$D$37,$D$38,0)</f>
+        <f>IF(1=$D$47,$D$48,0)</f>
         <v/>
       </c>
       <c r="F82" s="18">
-        <f>IF(2=$D$37,$D$38,0)</f>
+        <f>IF(2=$D$47,$D$48,0)</f>
         <v/>
       </c>
       <c r="G82" s="18">
-        <f>IF(3=$D$37,$D$38,0)</f>
+        <f>IF(3=$D$47,$D$48,0)</f>
         <v/>
       </c>
       <c r="H82" s="18">
-        <f>IF(4=$D$37,$D$38,0)</f>
+        <f>IF(4=$D$47,$D$48,0)</f>
         <v/>
       </c>
       <c r="I82" s="18">
-        <f>IF(5=$D$37,$D$38,0)</f>
+        <f>IF(5=$D$47,$D$48,0)</f>
         <v/>
       </c>
       <c r="J82" s="18">
-        <f>IF(6=$D$37,$D$38,0)</f>
+        <f>IF(6=$D$47,$D$48,0)</f>
         <v/>
       </c>
       <c r="K82" s="18">
-        <f>IF(7=$D$37,$D$38,0)</f>
+        <f>IF(7=$D$47,$D$48,0)</f>
         <v/>
       </c>
       <c r="L82" s="18">
-        <f>IF(8=$D$37,$D$38,0)</f>
+        <f>IF(8=$D$47,$D$48,0)</f>
         <v/>
       </c>
       <c r="M82" s="18">
-        <f>IF(9=$D$37,$D$38,0)</f>
+        <f>IF(9=$D$47,$D$48,0)</f>
         <v/>
       </c>
       <c r="N82" s="18">
-        <f>IF(10=$D$37,$D$38,0)</f>
+        <f>IF(10=$D$47,$D$48,0)</f>
         <v/>
       </c>
     </row>
@@ -5044,47 +5031,46 @@
         </is>
       </c>
       <c r="E83" s="7">
-        <f>E68-E71-E72</f>
+        <f>E78-E81-E82</f>
         <v/>
       </c>
       <c r="F83" s="7">
-        <f>F68-F71-F72</f>
+        <f>F78-F81-F82</f>
         <v/>
       </c>
       <c r="G83" s="7">
-        <f>G68-G71-G72</f>
+        <f>G78-G81-G82</f>
         <v/>
       </c>
       <c r="H83" s="7">
-        <f>H68-H71-H72</f>
+        <f>H78-H81-H82</f>
         <v/>
       </c>
       <c r="I83" s="7">
-        <f>I68-I71-I72</f>
+        <f>I78-I81-I82</f>
         <v/>
       </c>
       <c r="J83" s="7">
-        <f>J68-J71-J72</f>
+        <f>J78-J81-J82</f>
         <v/>
       </c>
       <c r="K83" s="7">
-        <f>K68-K71-K72</f>
+        <f>K78-K81-K82</f>
         <v/>
       </c>
       <c r="L83" s="7">
-        <f>L68-L71-L72</f>
+        <f>L78-L81-L82</f>
         <v/>
       </c>
       <c r="M83" s="7">
-        <f>M68-M71-M72</f>
+        <f>M78-M81-M82</f>
         <v/>
       </c>
       <c r="N83" s="7">
-        <f>N68-N71-N72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84"/>
+        <f>N78-N81-N82</f>
+        <v/>
+      </c>
+    </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
@@ -5121,44 +5107,47 @@
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr"/>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
       <c r="E86" s="16">
-        <f>$D$55</f>
+        <f>$D$65</f>
         <v/>
       </c>
       <c r="F86" s="16">
-        <f>E81</f>
+        <f>E91</f>
         <v/>
       </c>
       <c r="G86" s="16">
-        <f>F81</f>
+        <f>F91</f>
         <v/>
       </c>
       <c r="H86" s="16">
-        <f>G81</f>
+        <f>G91</f>
         <v/>
       </c>
       <c r="I86" s="16">
-        <f>H81</f>
+        <f>H91</f>
         <v/>
       </c>
       <c r="J86" s="16">
-        <f>I81</f>
+        <f>I91</f>
         <v/>
       </c>
       <c r="K86" s="16">
-        <f>J81</f>
+        <f>J91</f>
         <v/>
       </c>
       <c r="L86" s="16">
-        <f>K81</f>
+        <f>K91</f>
         <v/>
       </c>
       <c r="M86" s="16">
-        <f>L81</f>
+        <f>L91</f>
         <v/>
       </c>
       <c r="N86" s="16">
-        <f>M81</f>
+        <f>M91</f>
         <v/>
       </c>
     </row>
@@ -5179,43 +5168,43 @@
         </is>
       </c>
       <c r="E87" s="16">
-        <f>E76*$D$42</f>
+        <f>E86*$D$52</f>
         <v/>
       </c>
       <c r="F87" s="16">
-        <f>F76*$D$42</f>
+        <f>F86*$D$52</f>
         <v/>
       </c>
       <c r="G87" s="16">
-        <f>G76*$D$42</f>
+        <f>G86*$D$52</f>
         <v/>
       </c>
       <c r="H87" s="16">
-        <f>H76*$D$42</f>
+        <f>H86*$D$52</f>
         <v/>
       </c>
       <c r="I87" s="16">
-        <f>I76*$D$42</f>
+        <f>I86*$D$52</f>
         <v/>
       </c>
       <c r="J87" s="16">
-        <f>J76*$D$42</f>
+        <f>J86*$D$52</f>
         <v/>
       </c>
       <c r="K87" s="16">
-        <f>K76*$D$42</f>
+        <f>K86*$D$52</f>
         <v/>
       </c>
       <c r="L87" s="16">
-        <f>L76*$D$42</f>
+        <f>L86*$D$52</f>
         <v/>
       </c>
       <c r="M87" s="16">
-        <f>M76*$D$42</f>
+        <f>M86*$D$52</f>
         <v/>
       </c>
       <c r="N87" s="16">
-        <f>N76*$D$42</f>
+        <f>N86*$D$52</f>
         <v/>
       </c>
     </row>
@@ -5236,43 +5225,43 @@
         </is>
       </c>
       <c r="E88" s="16">
-        <f>E73/$D$45</f>
+        <f>E83/$D$55</f>
         <v/>
       </c>
       <c r="F88" s="16">
-        <f>F73/$D$45</f>
+        <f>F83/$D$55</f>
         <v/>
       </c>
       <c r="G88" s="16">
-        <f>G73/$D$45</f>
+        <f>G83/$D$55</f>
         <v/>
       </c>
       <c r="H88" s="16">
-        <f>H73/$D$45</f>
+        <f>H83/$D$55</f>
         <v/>
       </c>
       <c r="I88" s="16">
-        <f>I73/$D$45</f>
+        <f>I83/$D$55</f>
         <v/>
       </c>
       <c r="J88" s="16">
-        <f>J73/$D$45</f>
+        <f>J83/$D$55</f>
         <v/>
       </c>
       <c r="K88" s="16">
-        <f>K73/$D$45</f>
+        <f>K83/$D$55</f>
         <v/>
       </c>
       <c r="L88" s="16">
-        <f>L73/$D$45</f>
+        <f>L83/$D$55</f>
         <v/>
       </c>
       <c r="M88" s="16">
-        <f>M73/$D$45</f>
+        <f>M83/$D$55</f>
         <v/>
       </c>
       <c r="N88" s="16">
-        <f>N73/$D$45</f>
+        <f>N83/$D$55</f>
         <v/>
       </c>
     </row>
@@ -5293,43 +5282,43 @@
         </is>
       </c>
       <c r="E89" s="16">
-        <f>MIN(MAX(0,E78-E77),E76)</f>
+        <f>MIN(MAX(0,E88-E87),E86)</f>
         <v/>
       </c>
       <c r="F89" s="16">
-        <f>MIN(MAX(0,F78-F77),F76)</f>
+        <f>MIN(MAX(0,F88-F87),F86)</f>
         <v/>
       </c>
       <c r="G89" s="16">
-        <f>MIN(MAX(0,G78-G77),G76)</f>
+        <f>MIN(MAX(0,G88-G87),G86)</f>
         <v/>
       </c>
       <c r="H89" s="16">
-        <f>MIN(MAX(0,H78-H77),H76)</f>
+        <f>MIN(MAX(0,H88-H87),H86)</f>
         <v/>
       </c>
       <c r="I89" s="16">
-        <f>MIN(MAX(0,I78-I77),I76)</f>
+        <f>MIN(MAX(0,I88-I87),I86)</f>
         <v/>
       </c>
       <c r="J89" s="16">
-        <f>MIN(MAX(0,J78-J77),J76)</f>
+        <f>MIN(MAX(0,J88-J87),J86)</f>
         <v/>
       </c>
       <c r="K89" s="16">
-        <f>MIN(MAX(0,K78-K77),K76)</f>
+        <f>MIN(MAX(0,K88-K87),K86)</f>
         <v/>
       </c>
       <c r="L89" s="16">
-        <f>MIN(MAX(0,L78-L77),L76)</f>
+        <f>MIN(MAX(0,L88-L87),L86)</f>
         <v/>
       </c>
       <c r="M89" s="16">
-        <f>MIN(MAX(0,M78-M77),M76)</f>
+        <f>MIN(MAX(0,M88-M87),M86)</f>
         <v/>
       </c>
       <c r="N89" s="16">
-        <f>MIN(MAX(0,N78-N77),N76)</f>
+        <f>MIN(MAX(0,N88-N87),N86)</f>
         <v/>
       </c>
     </row>
@@ -5350,43 +5339,43 @@
         </is>
       </c>
       <c r="E90" s="16">
-        <f>E77+E79</f>
+        <f>E87+E89</f>
         <v/>
       </c>
       <c r="F90" s="16">
-        <f>F77+F79</f>
+        <f>F87+F89</f>
         <v/>
       </c>
       <c r="G90" s="16">
-        <f>G77+G79</f>
+        <f>G87+G89</f>
         <v/>
       </c>
       <c r="H90" s="16">
-        <f>H77+H79</f>
+        <f>H87+H89</f>
         <v/>
       </c>
       <c r="I90" s="16">
-        <f>I77+I79</f>
+        <f>I87+I89</f>
         <v/>
       </c>
       <c r="J90" s="16">
-        <f>J77+J79</f>
+        <f>J87+J89</f>
         <v/>
       </c>
       <c r="K90" s="16">
-        <f>K77+K79</f>
+        <f>K87+K89</f>
         <v/>
       </c>
       <c r="L90" s="16">
-        <f>L77+L79</f>
+        <f>L87+L89</f>
         <v/>
       </c>
       <c r="M90" s="16">
-        <f>M77+M79</f>
+        <f>M87+M89</f>
         <v/>
       </c>
       <c r="N90" s="16">
-        <f>N77+N79</f>
+        <f>N87+N89</f>
         <v/>
       </c>
     </row>
@@ -5406,44 +5395,48 @@
           <t>Beg - Principal</t>
         </is>
       </c>
+      <c r="D91">
+        <f>$D$65</f>
+        <v/>
+      </c>
       <c r="E91" s="16">
-        <f>MAX(0,E76-E79)</f>
+        <f>MAX(0,E86-E89)</f>
         <v/>
       </c>
       <c r="F91" s="16">
-        <f>MAX(0,F76-F79)</f>
+        <f>MAX(0,F86-F89)</f>
         <v/>
       </c>
       <c r="G91" s="16">
-        <f>MAX(0,G76-G79)</f>
+        <f>MAX(0,G86-G89)</f>
         <v/>
       </c>
       <c r="H91" s="16">
-        <f>MAX(0,H76-H79)</f>
+        <f>MAX(0,H86-H89)</f>
         <v/>
       </c>
       <c r="I91" s="16">
-        <f>MAX(0,I76-I79)</f>
+        <f>MAX(0,I86-I89)</f>
         <v/>
       </c>
       <c r="J91" s="16">
-        <f>MAX(0,J76-J79)</f>
+        <f>MAX(0,J86-J89)</f>
         <v/>
       </c>
       <c r="K91" s="16">
-        <f>MAX(0,K76-K79)</f>
+        <f>MAX(0,K86-K89)</f>
         <v/>
       </c>
       <c r="L91" s="16">
-        <f>MAX(0,L76-L79)</f>
+        <f>MAX(0,L86-L89)</f>
         <v/>
       </c>
       <c r="M91" s="16">
-        <f>MAX(0,M76-M79)</f>
+        <f>MAX(0,M86-M89)</f>
         <v/>
       </c>
       <c r="N91" s="16">
-        <f>MAX(0,N76-N79)</f>
+        <f>MAX(0,N86-N89)</f>
         <v/>
       </c>
     </row>
@@ -5464,47 +5457,46 @@
         </is>
       </c>
       <c r="E92" s="21">
-        <f>IF(E80&gt;0,E73/E80,0)</f>
+        <f>IF(E90&gt;0,E83/E90,0)</f>
         <v/>
       </c>
       <c r="F92" s="21">
-        <f>IF(F80&gt;0,F73/F80,0)</f>
+        <f>IF(F90&gt;0,F83/F90,0)</f>
         <v/>
       </c>
       <c r="G92" s="21">
-        <f>IF(G80&gt;0,G73/G80,0)</f>
+        <f>IF(G90&gt;0,G83/G90,0)</f>
         <v/>
       </c>
       <c r="H92" s="21">
-        <f>IF(H80&gt;0,H73/H80,0)</f>
+        <f>IF(H90&gt;0,H83/H90,0)</f>
         <v/>
       </c>
       <c r="I92" s="21">
-        <f>IF(I80&gt;0,I73/I80,0)</f>
+        <f>IF(I90&gt;0,I83/I90,0)</f>
         <v/>
       </c>
       <c r="J92" s="21">
-        <f>IF(J80&gt;0,J73/J80,0)</f>
+        <f>IF(J90&gt;0,J83/J90,0)</f>
         <v/>
       </c>
       <c r="K92" s="21">
-        <f>IF(K80&gt;0,K73/K80,0)</f>
+        <f>IF(K90&gt;0,K83/K90,0)</f>
         <v/>
       </c>
       <c r="L92" s="21">
-        <f>IF(L80&gt;0,L73/L80,0)</f>
+        <f>IF(L90&gt;0,L83/L90,0)</f>
         <v/>
       </c>
       <c r="M92" s="21">
-        <f>IF(M80&gt;0,M73/M80,0)</f>
+        <f>IF(M90&gt;0,M83/M90,0)</f>
         <v/>
       </c>
       <c r="N92" s="21">
-        <f>IF(N80&gt;0,N73/N80,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93"/>
+        <f>IF(N90&gt;0,N83/N90,0)</f>
+        <v/>
+      </c>
+    </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
@@ -5546,44 +5538,43 @@
         <v/>
       </c>
       <c r="E95" s="16">
-        <f>F80*$D$44/12</f>
+        <f>F90*$D$54/12</f>
         <v/>
       </c>
       <c r="F95" s="16">
-        <f>G80*$D$44/12</f>
+        <f>G90*$D$54/12</f>
         <v/>
       </c>
       <c r="G95" s="16">
-        <f>H80*$D$44/12</f>
+        <f>H90*$D$54/12</f>
         <v/>
       </c>
       <c r="H95" s="16">
-        <f>I80*$D$44/12</f>
+        <f>I90*$D$54/12</f>
         <v/>
       </c>
       <c r="I95" s="16">
-        <f>J80*$D$44/12</f>
+        <f>J90*$D$54/12</f>
         <v/>
       </c>
       <c r="J95" s="16">
-        <f>K80*$D$44/12</f>
+        <f>K90*$D$54/12</f>
         <v/>
       </c>
       <c r="K95" s="16">
-        <f>L80*$D$44/12</f>
+        <f>L90*$D$54/12</f>
         <v/>
       </c>
       <c r="L95" s="16">
-        <f>M80*$D$44/12</f>
+        <f>M90*$D$54/12</f>
         <v/>
       </c>
       <c r="M95" s="16">
-        <f>N80*$D$44/12</f>
-        <v/>
-      </c>
-      <c r="N95" s="16">
-        <f>0</f>
-        <v/>
+        <f>N90*$D$54/12</f>
+        <v/>
+      </c>
+      <c r="N95" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -5598,48 +5589,47 @@
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr"/>
-      <c r="D96" s="16">
-        <f>0</f>
-        <v/>
+      <c r="D96" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="E96" s="16">
-        <f>D88</f>
+        <f>D109</f>
         <v/>
       </c>
       <c r="F96" s="16">
-        <f>E88</f>
+        <f>E98</f>
         <v/>
       </c>
       <c r="G96" s="16">
-        <f>F88</f>
+        <f>F98</f>
         <v/>
       </c>
       <c r="H96" s="16">
-        <f>G88</f>
+        <f>G98</f>
         <v/>
       </c>
       <c r="I96" s="16">
-        <f>H88</f>
+        <f>H98</f>
         <v/>
       </c>
       <c r="J96" s="16">
-        <f>I88</f>
+        <f>I98</f>
         <v/>
       </c>
       <c r="K96" s="16">
-        <f>J88</f>
+        <f>J98</f>
         <v/>
       </c>
       <c r="L96" s="16">
-        <f>K88</f>
+        <f>K98</f>
         <v/>
       </c>
       <c r="M96" s="16">
-        <f>L88</f>
+        <f>L98</f>
         <v/>
       </c>
       <c r="N96" s="16">
-        <f>M88</f>
+        <f>M98</f>
         <v/>
       </c>
     </row>
@@ -5664,43 +5654,43 @@
         <v/>
       </c>
       <c r="E97" s="16">
-        <f>E85-E86</f>
+        <f>E95-E96</f>
         <v/>
       </c>
       <c r="F97" s="16">
-        <f>F85-F86</f>
+        <f>F95-F96</f>
         <v/>
       </c>
       <c r="G97" s="16">
-        <f>G85-G86</f>
+        <f>G95-G96</f>
         <v/>
       </c>
       <c r="H97" s="16">
-        <f>H85-H86</f>
+        <f>H95-H96</f>
         <v/>
       </c>
       <c r="I97" s="16">
-        <f>I85-I86</f>
+        <f>I95-I96</f>
         <v/>
       </c>
       <c r="J97" s="16">
-        <f>J85-J86</f>
+        <f>J95-J96</f>
         <v/>
       </c>
       <c r="K97" s="16">
-        <f>K85-K86</f>
+        <f>K95-K96</f>
         <v/>
       </c>
       <c r="L97" s="16">
-        <f>L85-L86</f>
+        <f>L95-L96</f>
         <v/>
       </c>
       <c r="M97" s="16">
-        <f>M85-M86</f>
+        <f>M95-M96</f>
         <v/>
       </c>
       <c r="N97" s="16">
-        <f>N85-N86</f>
+        <f>N95-N96</f>
         <v/>
       </c>
     </row>
@@ -5725,47 +5715,46 @@
         <v/>
       </c>
       <c r="E98" s="16">
-        <f>E86+E87</f>
+        <f>E96+E97</f>
         <v/>
       </c>
       <c r="F98" s="16">
-        <f>F86+F87</f>
+        <f>F96+F97</f>
         <v/>
       </c>
       <c r="G98" s="16">
-        <f>G86+G87</f>
+        <f>G96+G97</f>
         <v/>
       </c>
       <c r="H98" s="16">
-        <f>H86+H87</f>
+        <f>H96+H97</f>
         <v/>
       </c>
       <c r="I98" s="16">
-        <f>I86+I87</f>
+        <f>I96+I97</f>
         <v/>
       </c>
       <c r="J98" s="16">
-        <f>J86+J87</f>
+        <f>J96+J97</f>
         <v/>
       </c>
       <c r="K98" s="16">
-        <f>K86+K87</f>
+        <f>K96+K97</f>
         <v/>
       </c>
       <c r="L98" s="16">
-        <f>L86+L87</f>
+        <f>L96+L97</f>
         <v/>
       </c>
       <c r="M98" s="16">
-        <f>M86+M87</f>
+        <f>M96+M97</f>
         <v/>
       </c>
       <c r="N98" s="16">
-        <f>N86+N87</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99"/>
+        <f>N96+N97</f>
+        <v/>
+      </c>
+    </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
@@ -5803,43 +5792,43 @@
         </is>
       </c>
       <c r="E101" s="16">
-        <f>E73-E80-E87</f>
+        <f>E83-E90-E97</f>
         <v/>
       </c>
       <c r="F101" s="16">
-        <f>F73-F80-F87</f>
+        <f>F83-F90-F97</f>
         <v/>
       </c>
       <c r="G101" s="16">
-        <f>G73-G80-G87</f>
+        <f>G83-G90-G97</f>
         <v/>
       </c>
       <c r="H101" s="16">
-        <f>H73-H80-H87</f>
+        <f>H83-H90-H97</f>
         <v/>
       </c>
       <c r="I101" s="16">
-        <f>I73-I80-I87</f>
+        <f>I83-I90-I97</f>
         <v/>
       </c>
       <c r="J101" s="16">
-        <f>J73-J80-J87</f>
+        <f>J83-J90-J97</f>
         <v/>
       </c>
       <c r="K101" s="16">
-        <f>K73-K80-K87</f>
+        <f>K83-K90-K97</f>
         <v/>
       </c>
       <c r="L101" s="16">
-        <f>L73-L80-L87</f>
+        <f>L83-L90-L97</f>
         <v/>
       </c>
       <c r="M101" s="16">
-        <f>M73-M80-M87</f>
+        <f>M83-M90-M97</f>
         <v/>
       </c>
       <c r="N101" s="16">
-        <f>N73-N80-N87</f>
+        <f>N83-N90-N97</f>
         <v/>
       </c>
     </row>
@@ -5856,43 +5845,43 @@
         </is>
       </c>
       <c r="E102" s="19">
-        <f>IF(E82&gt;=$D$46,"PASS","LOCKED")</f>
+        <f>IF(E92&gt;=$D$56,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="F102" s="19">
-        <f>IF(F82&gt;=$D$46,"PASS","LOCKED")</f>
+        <f>IF(F92&gt;=$D$56,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="G102" s="19">
-        <f>IF(G82&gt;=$D$46,"PASS","LOCKED")</f>
+        <f>IF(G92&gt;=$D$56,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="H102" s="19">
-        <f>IF(H82&gt;=$D$46,"PASS","LOCKED")</f>
+        <f>IF(H92&gt;=$D$56,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="I102" s="19">
-        <f>IF(I82&gt;=$D$46,"PASS","LOCKED")</f>
+        <f>IF(I92&gt;=$D$56,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="J102" s="19">
-        <f>IF(J82&gt;=$D$46,"PASS","LOCKED")</f>
+        <f>IF(J92&gt;=$D$56,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="K102" s="19">
-        <f>IF(K82&gt;=$D$46,"PASS","LOCKED")</f>
+        <f>IF(K92&gt;=$D$56,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="L102" s="19">
-        <f>IF(L82&gt;=$D$46,"PASS","LOCKED")</f>
+        <f>IF(L92&gt;=$D$56,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="M102" s="19">
-        <f>IF(M82&gt;=$D$46,"PASS","LOCKED")</f>
+        <f>IF(M92&gt;=$D$56,"PASS","LOCKED")</f>
         <v/>
       </c>
       <c r="N102" s="19">
-        <f>IF(N82&gt;=$D$46,"PASS","LOCKED")</f>
+        <f>IF(N92&gt;=$D$56,"PASS","LOCKED")</f>
         <v/>
       </c>
     </row>
@@ -5913,47 +5902,46 @@
         </is>
       </c>
       <c r="E103" s="7">
-        <f>IF(E92="PASS",MAX(0,E91),0)</f>
+        <f>IF(E102="PASS",MAX(0,E101),0)</f>
         <v/>
       </c>
       <c r="F103" s="7">
-        <f>IF(F92="PASS",MAX(0,F91),0)</f>
+        <f>IF(F102="PASS",MAX(0,F101),0)</f>
         <v/>
       </c>
       <c r="G103" s="7">
-        <f>IF(G92="PASS",MAX(0,G91),0)</f>
+        <f>IF(G102="PASS",MAX(0,G101),0)</f>
         <v/>
       </c>
       <c r="H103" s="7">
-        <f>IF(H92="PASS",MAX(0,H91),0)</f>
+        <f>IF(H102="PASS",MAX(0,H101),0)</f>
         <v/>
       </c>
       <c r="I103" s="7">
-        <f>IF(I92="PASS",MAX(0,I91),0)</f>
+        <f>IF(I102="PASS",MAX(0,I101),0)</f>
         <v/>
       </c>
       <c r="J103" s="7">
-        <f>IF(J92="PASS",MAX(0,J91),0)</f>
+        <f>IF(J102="PASS",MAX(0,J101),0)</f>
         <v/>
       </c>
       <c r="K103" s="7">
-        <f>IF(K92="PASS",MAX(0,K91),0)</f>
+        <f>IF(K102="PASS",MAX(0,K101),0)</f>
         <v/>
       </c>
       <c r="L103" s="7">
-        <f>IF(L92="PASS",MAX(0,L91),0)</f>
+        <f>IF(L102="PASS",MAX(0,L101),0)</f>
         <v/>
       </c>
       <c r="M103" s="7">
-        <f>IF(M92="PASS",MAX(0,M91),0)</f>
+        <f>IF(M102="PASS",MAX(0,M101),0)</f>
         <v/>
       </c>
       <c r="N103" s="7">
-        <f>IF(N92="PASS",MAX(0,N91),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104"/>
+        <f>IF(N102="PASS",MAX(0,N101),0)</f>
+        <v/>
+      </c>
+    </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
@@ -5996,7 +5984,7 @@
       </c>
       <c r="C107" s="6" t="inlineStr"/>
       <c r="D107" s="16">
-        <f>$D$17</f>
+        <f>$D$27</f>
         <v/>
       </c>
     </row>
@@ -6013,7 +6001,7 @@
       </c>
       <c r="C108" s="6" t="inlineStr"/>
       <c r="D108" s="16">
-        <f>$D$17*$D$18</f>
+        <f>$D$27*$D$28</f>
         <v/>
       </c>
     </row>
@@ -6030,7 +6018,7 @@
       </c>
       <c r="C109" s="6" t="inlineStr"/>
       <c r="D109" s="16">
-        <f>D85</f>
+        <f>E95</f>
         <v/>
       </c>
     </row>
@@ -6047,11 +6035,10 @@
       </c>
       <c r="C110" s="6" t="inlineStr"/>
       <c r="D110" s="7">
-        <f>D97+D98+D99</f>
-        <v/>
-      </c>
-    </row>
-    <row r="111"/>
+        <f>D107+D108+D109</f>
+        <v/>
+      </c>
+    </row>
     <row r="112">
       <c r="A112" s="20" t="inlineStr">
         <is>
@@ -6074,7 +6061,7 @@
       </c>
       <c r="C113" s="6" t="inlineStr"/>
       <c r="D113" s="16">
-        <f>$D$55</f>
+        <f>$D$27*$D$51</f>
         <v/>
       </c>
     </row>
@@ -6095,7 +6082,7 @@
         </is>
       </c>
       <c r="D114" s="16">
-        <f>D100-D103</f>
+        <f>D110-D113</f>
         <v/>
       </c>
     </row>
@@ -6116,7 +6103,7 @@
         </is>
       </c>
       <c r="D115" s="16">
-        <f>$D$56</f>
+        <f>$D$66</f>
         <v/>
       </c>
     </row>
@@ -6137,7 +6124,7 @@
         </is>
       </c>
       <c r="D116" s="7">
-        <f>D104-D105</f>
+        <f>D114-D115</f>
         <v/>
       </c>
     </row>
@@ -6154,7 +6141,7 @@
       </c>
       <c r="C117" s="6" t="inlineStr"/>
       <c r="D117" s="7">
-        <f>D103+D106+D105</f>
+        <f>D113+D116+D115</f>
         <v/>
       </c>
     </row>
@@ -6167,11 +6154,10 @@
       <c r="B118" s="6" t="inlineStr"/>
       <c r="C118" s="6" t="inlineStr"/>
       <c r="D118" s="10">
-        <f>IF(ABS(D100-D107)&lt;0.01,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="119"/>
+        <f>IF(ABS(D110-D117)&lt;0.01,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
@@ -6208,6 +6194,10 @@
           <t>Exit Multiple × Exit Yr EBITDA</t>
         </is>
       </c>
+      <c r="D121">
+        <f>N78*$D$30</f>
+        <v/>
+      </c>
       <c r="N121" s="16">
         <f>$D$20*N68</f>
         <v/>
@@ -6229,6 +6219,10 @@
           <t>Ending Bal at Exit</t>
         </is>
       </c>
+      <c r="D122">
+        <f>N91</f>
+        <v/>
+      </c>
       <c r="N122" s="16">
         <f>N81</f>
         <v/>
@@ -6250,6 +6244,10 @@
           <t>DSRA Ending at Exit</t>
         </is>
       </c>
+      <c r="D123">
+        <f>N98</f>
+        <v/>
+      </c>
       <c r="N123" s="16">
         <f>N88</f>
         <v/>
@@ -6271,12 +6269,15 @@
           <t>Exit EV - Debt + DSRA</t>
         </is>
       </c>
+      <c r="D124">
+        <f>D121-D122+D123</f>
+        <v/>
+      </c>
       <c r="N124" s="7">
         <f>N111-N112+N113</f>
         <v/>
       </c>
     </row>
-    <row r="125"/>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
@@ -6310,47 +6311,47 @@
       </c>
       <c r="C127" s="6" t="inlineStr"/>
       <c r="D127" s="16">
-        <f>-D106</f>
+        <f>-D116</f>
         <v/>
       </c>
       <c r="E127" s="16">
-        <f>E93</f>
+        <f>E103</f>
         <v/>
       </c>
       <c r="F127" s="16">
-        <f>F93</f>
+        <f>F103</f>
         <v/>
       </c>
       <c r="G127" s="16">
-        <f>G93</f>
+        <f>G103</f>
         <v/>
       </c>
       <c r="H127" s="16">
-        <f>H93</f>
+        <f>H103</f>
         <v/>
       </c>
       <c r="I127" s="16">
-        <f>I93</f>
+        <f>I103</f>
         <v/>
       </c>
       <c r="J127" s="16">
-        <f>J93</f>
+        <f>J103</f>
         <v/>
       </c>
       <c r="K127" s="16">
-        <f>K93</f>
+        <f>K103</f>
         <v/>
       </c>
       <c r="L127" s="16">
-        <f>L93</f>
+        <f>L103</f>
         <v/>
       </c>
       <c r="M127" s="16">
-        <f>M93</f>
+        <f>M103</f>
         <v/>
       </c>
       <c r="N127" s="16">
-        <f>N93+N114</f>
+        <f>N103+D124</f>
         <v/>
       </c>
     </row>
@@ -6371,7 +6372,7 @@
         </is>
       </c>
       <c r="D128" s="22">
-        <f>IRR(D117:N117)</f>
+        <f>IRR(D127:N127)</f>
         <v/>
       </c>
     </row>
@@ -6392,11 +6393,10 @@
         </is>
       </c>
       <c r="D129" s="21">
-        <f>SUMIF(D117:N117,"&gt;0")/ABS(D117)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130"/>
+        <f>(SUM(E127:N127))/-D127</f>
+        <v/>
+      </c>
+    </row>
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
@@ -6419,47 +6419,47 @@
       </c>
       <c r="C132" s="6" t="inlineStr"/>
       <c r="D132" s="16">
-        <f>-$D$17-D98</f>
+        <f>-$D$27-D108</f>
         <v/>
       </c>
       <c r="E132" s="16">
-        <f>E73</f>
+        <f>E83</f>
         <v/>
       </c>
       <c r="F132" s="16">
-        <f>F73</f>
+        <f>F83</f>
         <v/>
       </c>
       <c r="G132" s="16">
-        <f>G73</f>
+        <f>G83</f>
         <v/>
       </c>
       <c r="H132" s="16">
-        <f>H73</f>
+        <f>H83</f>
         <v/>
       </c>
       <c r="I132" s="16">
-        <f>I73</f>
+        <f>I83</f>
         <v/>
       </c>
       <c r="J132" s="16">
-        <f>J73</f>
+        <f>J83</f>
         <v/>
       </c>
       <c r="K132" s="16">
-        <f>K73</f>
+        <f>K83</f>
         <v/>
       </c>
       <c r="L132" s="16">
-        <f>L73</f>
+        <f>L83</f>
         <v/>
       </c>
       <c r="M132" s="16">
-        <f>M73</f>
+        <f>M83</f>
         <v/>
       </c>
       <c r="N132" s="16">
-        <f>N73+N111</f>
+        <f>N83+D121</f>
         <v/>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
         </is>
       </c>
       <c r="D133" s="22">
-        <f>IRR(D122:N122)</f>
+        <f>IRR(D132:N132)</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Model_3_SolarBESS.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_3_SolarBESS.xlsx
@@ -3741,7 +3741,7 @@
       <c r="B22" s="6" t="inlineStr"/>
       <c r="C22" s="6" t="inlineStr"/>
       <c r="D22" s="10">
-        <f>IF(N81&lt;1,"PASS","FAIL")</f>
+        <f>IF(N91&lt;1,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Model_3_SolarBESS.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_3_SolarBESS.xlsx
@@ -3727,10 +3727,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr"/>
       <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="10">
-        <f>D108</f>
-        <v/>
-      </c>
+      <c r="D21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -3758,7 +3755,7 @@
         </is>
       </c>
       <c r="D23" s="10">
-        <f>IF(D6&gt;=1.30,"PASS","FAIL")</f>
+        <f>IF(MINIFS(E92:N92,E92:N92,"&gt;0")&gt;=1.3,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Model_3_SolarBESS.xlsx
+++ b/deliverables/deliverables-20260120-0030/Model_3_SolarBESS.xlsx
@@ -170,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -241,6 +241,7 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3526,10 +3527,25 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="44" t="n"/>
-      <c r="B6" s="44" t="n"/>
-      <c r="C6" s="44" t="n"/>
-      <c r="D6" s="44" t="n"/>
+      <c r="A6" s="44" t="inlineStr">
+        <is>
+          <t>Min DSCR</t>
+        </is>
+      </c>
+      <c r="B6" s="44" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C6" s="44" t="inlineStr">
+        <is>
+          <t>Minimum debt service coverage ratio</t>
+        </is>
+      </c>
+      <c r="D6" s="52">
+        <f>IF(COUNTIF(E92:N92,"&gt;0")&gt;0,MINIFS(E92:N92,E92:N92,"&gt;0"),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="45" t="inlineStr">
@@ -3755,7 +3771,7 @@
         </is>
       </c>
       <c r="D23" s="10">
-        <f>IF(MINIFS(E92:N92,E92:N92,"&gt;0")&gt;=1.3,"PASS","FAIL")</f>
+        <f>IF(D6&gt;=1.3,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
